--- a/research/traditional_assets/database/data/poland/poland_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_oilfield_svcs_equip.xlsx
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08944143580322035</v>
+        <v>0.08930794707519424</v>
       </c>
       <c r="C2">
-        <v>18553.21089709359</v>
+        <v>18409.7770580519</v>
       </c>
       <c r="D2">
-        <v>15734.31089709359</v>
+        <v>15782.58605805189</v>
       </c>
       <c r="E2">
-        <v>-5912.6</v>
+        <v>-5720.891000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>191.709</v>
       </c>
       <c r="G2">
         <v>2818.9</v>
@@ -1585,28 +1585,28 @@
         <v>10511.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>9.642962700000002</v>
       </c>
       <c r="N2">
-        <v>10511.5</v>
+        <v>10501.8570373</v>
       </c>
       <c r="O2">
-        <v>1997.185</v>
+        <v>1995.352837087</v>
       </c>
       <c r="P2">
-        <v>8514.315000000001</v>
+        <v>8506.504200212999</v>
       </c>
       <c r="Q2">
-        <v>8898.815000000001</v>
+        <v>8891.004200212999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08944143580322035</v>
+        <v>0.08979850209615579</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8058480175267986</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>1090.069548853487</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08930794707519424</v>
+        <v>0.08917445834716811</v>
       </c>
       <c r="C3">
-        <v>18409.7770580519</v>
+        <v>18266.64036115685</v>
       </c>
       <c r="D3">
-        <v>15782.58605805189</v>
+        <v>15831.15836115685</v>
       </c>
       <c r="E3">
-        <v>-5720.891000000001</v>
+        <v>-5529.182000000001</v>
       </c>
       <c r="F3">
-        <v>191.709</v>
+        <v>383.4180000000001</v>
       </c>
       <c r="G3">
         <v>2818.9</v>
@@ -1667,28 +1667,28 @@
         <v>10511.5</v>
       </c>
       <c r="M3">
-        <v>9.642962700000002</v>
+        <v>19.2859254</v>
       </c>
       <c r="N3">
-        <v>10501.8570373</v>
+        <v>10492.2140746</v>
       </c>
       <c r="O3">
-        <v>1995.352837087</v>
+        <v>1993.520674174</v>
       </c>
       <c r="P3">
-        <v>8506.504200212999</v>
+        <v>8498.693400426</v>
       </c>
       <c r="Q3">
-        <v>8891.004200212999</v>
+        <v>8883.193400426</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08979850209615579</v>
+        <v>0.09016285545629399</v>
       </c>
       <c r="T3">
-        <v>0.8058480175267986</v>
+        <v>0.8125212772733446</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>1090.069548853487</v>
+        <v>545.0347744267433</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08917445834716811</v>
+        <v>0.089040969619142</v>
       </c>
       <c r="C4">
-        <v>18266.64036115685</v>
+        <v>18123.80355832136</v>
       </c>
       <c r="D4">
-        <v>15831.15836115685</v>
+        <v>15880.03055832136</v>
       </c>
       <c r="E4">
-        <v>-5529.182000000001</v>
+        <v>-5337.473</v>
       </c>
       <c r="F4">
-        <v>383.4180000000001</v>
+        <v>575.1270000000001</v>
       </c>
       <c r="G4">
         <v>2818.9</v>
@@ -1749,28 +1749,28 @@
         <v>10511.5</v>
       </c>
       <c r="M4">
-        <v>19.2859254</v>
+        <v>28.9288881</v>
       </c>
       <c r="N4">
-        <v>10492.2140746</v>
+        <v>10482.5711119</v>
       </c>
       <c r="O4">
-        <v>1993.520674174</v>
+        <v>1991.688511261</v>
       </c>
       <c r="P4">
-        <v>8498.693400426</v>
+        <v>8490.882600639001</v>
       </c>
       <c r="Q4">
-        <v>8883.193400426</v>
+        <v>8875.382600639001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09016285545629399</v>
+        <v>0.09053472125684742</v>
       </c>
       <c r="T4">
-        <v>0.8125212772733446</v>
+        <v>0.8193321300043556</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>545.0347744267433</v>
+        <v>363.3565162844956</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.089040969619142</v>
+        <v>0.08890748089111587</v>
       </c>
       <c r="C5">
-        <v>18123.80355832136</v>
+        <v>17981.26943554512</v>
       </c>
       <c r="D5">
-        <v>15880.03055832136</v>
+        <v>15929.20543554512</v>
       </c>
       <c r="E5">
-        <v>-5337.473</v>
+        <v>-5145.764</v>
       </c>
       <c r="F5">
-        <v>575.1270000000001</v>
+        <v>766.8360000000001</v>
       </c>
       <c r="G5">
         <v>2818.9</v>
@@ -1831,28 +1831,28 @@
         <v>10511.5</v>
       </c>
       <c r="M5">
-        <v>28.9288881</v>
+        <v>38.57185080000001</v>
       </c>
       <c r="N5">
-        <v>10482.5711119</v>
+        <v>10472.9281492</v>
       </c>
       <c r="O5">
-        <v>1991.688511261</v>
+        <v>1989.856348348</v>
       </c>
       <c r="P5">
-        <v>8490.882600639001</v>
+        <v>8483.071800852</v>
       </c>
       <c r="Q5">
-        <v>8875.382600639001</v>
+        <v>8867.571800852</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09053472125684742</v>
+        <v>0.09091433426157904</v>
       </c>
       <c r="T5">
-        <v>0.8193321300043556</v>
+        <v>0.8262848755005957</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>363.3565162844956</v>
+        <v>272.5173872133716</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08890748089111587</v>
+        <v>0.08877399216308975</v>
       </c>
       <c r="C6">
-        <v>17981.26943554512</v>
+        <v>17839.0408134441</v>
       </c>
       <c r="D6">
-        <v>15929.20543554512</v>
+        <v>15978.6858134441</v>
       </c>
       <c r="E6">
-        <v>-5145.764</v>
+        <v>-4954.055</v>
       </c>
       <c r="F6">
-        <v>766.8360000000001</v>
+        <v>958.5450000000001</v>
       </c>
       <c r="G6">
         <v>2818.9</v>
@@ -1913,28 +1913,28 @@
         <v>10511.5</v>
       </c>
       <c r="M6">
-        <v>38.57185080000001</v>
+        <v>48.2148135</v>
       </c>
       <c r="N6">
-        <v>10472.9281492</v>
+        <v>10463.2851865</v>
       </c>
       <c r="O6">
-        <v>1989.856348348</v>
+        <v>1988.024185435</v>
       </c>
       <c r="P6">
-        <v>8483.071800852</v>
+        <v>8475.261001064999</v>
       </c>
       <c r="Q6">
-        <v>8867.571800852</v>
+        <v>8859.761001064999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09091433426157904</v>
+        <v>0.09130193911904184</v>
       </c>
       <c r="T6">
-        <v>0.8262848755005957</v>
+        <v>0.8333839945862306</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>272.5173872133716</v>
+        <v>218.0139097706973</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08877399216308975</v>
+        <v>0.08864050343506363</v>
       </c>
       <c r="C7">
-        <v>17839.0408134441</v>
+        <v>17697.12054778983</v>
       </c>
       <c r="D7">
-        <v>15978.6858134441</v>
+        <v>16028.47454778983</v>
       </c>
       <c r="E7">
-        <v>-4954.055</v>
+        <v>-4762.346</v>
       </c>
       <c r="F7">
-        <v>958.5450000000001</v>
+        <v>1150.254</v>
       </c>
       <c r="G7">
         <v>2818.9</v>
@@ -1995,28 +1995,28 @@
         <v>10511.5</v>
       </c>
       <c r="M7">
-        <v>48.2148135</v>
+        <v>57.8577762</v>
       </c>
       <c r="N7">
-        <v>10463.2851865</v>
+        <v>10453.6422238</v>
       </c>
       <c r="O7">
-        <v>1988.024185435</v>
+        <v>1986.192022522</v>
       </c>
       <c r="P7">
-        <v>8475.261001064999</v>
+        <v>8467.450201277999</v>
       </c>
       <c r="Q7">
-        <v>8859.761001064999</v>
+        <v>8851.950201277999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09130193911904184</v>
+        <v>0.09169779088836558</v>
       </c>
       <c r="T7">
-        <v>0.8333839945862306</v>
+        <v>0.8406341587587938</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>218.0139097706973</v>
+        <v>181.6782581422478</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08864050343506363</v>
+        <v>0.08850701470703753</v>
       </c>
       <c r="C8">
-        <v>17697.12054778983</v>
+        <v>17555.5115300588</v>
       </c>
       <c r="D8">
-        <v>16028.47454778983</v>
+        <v>16078.5745300588</v>
       </c>
       <c r="E8">
-        <v>-4762.346</v>
+        <v>-4570.637000000001</v>
       </c>
       <c r="F8">
-        <v>1150.254</v>
+        <v>1341.963</v>
       </c>
       <c r="G8">
         <v>2818.9</v>
@@ -2077,28 +2077,28 @@
         <v>10511.5</v>
       </c>
       <c r="M8">
-        <v>57.8577762</v>
+        <v>67.5007389</v>
       </c>
       <c r="N8">
-        <v>10453.6422238</v>
+        <v>10443.9992611</v>
       </c>
       <c r="O8">
-        <v>1986.192022522</v>
+        <v>1984.359859609</v>
       </c>
       <c r="P8">
-        <v>8467.450201277999</v>
+        <v>8459.639401491</v>
       </c>
       <c r="Q8">
-        <v>8851.950201277999</v>
+        <v>8844.139401491</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09169779088836558</v>
+        <v>0.09210215559896508</v>
       </c>
       <c r="T8">
-        <v>0.8406341587587938</v>
+        <v>0.8480402404404446</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>181.6782581422478</v>
+        <v>155.7242212647838</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08850701470703752</v>
+        <v>0.08837352597901141</v>
       </c>
       <c r="C9">
-        <v>17555.5115300588</v>
+        <v>17414.21668799228</v>
       </c>
       <c r="D9">
-        <v>16078.5745300588</v>
+        <v>16128.98868799228</v>
       </c>
       <c r="E9">
-        <v>-4570.637000000001</v>
+        <v>-4378.928</v>
       </c>
       <c r="F9">
-        <v>1341.963</v>
+        <v>1533.672</v>
       </c>
       <c r="G9">
         <v>2818.9</v>
@@ -2159,28 +2159,28 @@
         <v>10511.5</v>
       </c>
       <c r="M9">
-        <v>67.5007389</v>
+        <v>77.14370160000001</v>
       </c>
       <c r="N9">
-        <v>10443.9992611</v>
+        <v>10434.3562984</v>
       </c>
       <c r="O9">
-        <v>1984.359859609</v>
+        <v>1982.527696696</v>
       </c>
       <c r="P9">
-        <v>8459.639401491</v>
+        <v>8451.828601704001</v>
       </c>
       <c r="Q9">
-        <v>8844.139401491</v>
+        <v>8836.328601704001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09210215559896508</v>
+        <v>0.09251531084675152</v>
       </c>
       <c r="T9">
-        <v>0.8480402404404446</v>
+        <v>0.8556073238977833</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>155.7242212647838</v>
+        <v>136.2586936066858</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08837352597901141</v>
+        <v>0.08824003725098528</v>
       </c>
       <c r="C10">
-        <v>17414.21668799228</v>
+        <v>17273.23898616657</v>
       </c>
       <c r="D10">
-        <v>16128.98868799228</v>
+        <v>16179.71998616657</v>
       </c>
       <c r="E10">
-        <v>-4378.928</v>
+        <v>-4187.219</v>
       </c>
       <c r="F10">
-        <v>1533.672</v>
+        <v>1725.381</v>
       </c>
       <c r="G10">
         <v>2818.9</v>
@@ -2241,28 +2241,28 @@
         <v>10511.5</v>
       </c>
       <c r="M10">
-        <v>77.14370160000001</v>
+        <v>86.7866643</v>
       </c>
       <c r="N10">
-        <v>10434.3562984</v>
+        <v>10424.7133357</v>
       </c>
       <c r="O10">
-        <v>1982.527696696</v>
+        <v>1980.695533783</v>
       </c>
       <c r="P10">
-        <v>8451.828601704001</v>
+        <v>8444.017801917</v>
       </c>
       <c r="Q10">
-        <v>8836.328601704001</v>
+        <v>8828.517801917</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09251531084675152</v>
+        <v>0.09293754642965416</v>
       </c>
       <c r="T10">
-        <v>0.8556073238977833</v>
+        <v>0.8633407168816567</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>136.2586936066858</v>
+        <v>121.1188387614985</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08824003725098528</v>
+        <v>0.08810654852295917</v>
       </c>
       <c r="C11">
-        <v>17273.23898616657</v>
+        <v>17132.58142657419</v>
       </c>
       <c r="D11">
-        <v>16179.71998616657</v>
+        <v>16230.77142657419</v>
       </c>
       <c r="E11">
-        <v>-4187.219</v>
+        <v>-3995.51</v>
       </c>
       <c r="F11">
-        <v>1725.381</v>
+        <v>1917.09</v>
       </c>
       <c r="G11">
         <v>2818.9</v>
@@ -2323,28 +2323,28 @@
         <v>10511.5</v>
       </c>
       <c r="M11">
-        <v>86.7866643</v>
+        <v>96.429627</v>
       </c>
       <c r="N11">
-        <v>10424.7133357</v>
+        <v>10415.070373</v>
       </c>
       <c r="O11">
-        <v>1980.695533783</v>
+        <v>1978.86337087</v>
       </c>
       <c r="P11">
-        <v>8444.017801917</v>
+        <v>8436.207002130001</v>
       </c>
       <c r="Q11">
-        <v>8828.517801917</v>
+        <v>8820.707002130001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09293754642965416</v>
+        <v>0.09336916502551018</v>
       </c>
       <c r="T11">
-        <v>0.8633407168816567</v>
+        <v>0.8712459630429499</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>121.1188387614985</v>
+        <v>109.0069548853487</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08810654852295917</v>
+        <v>0.08797305979493306</v>
       </c>
       <c r="C12">
-        <v>17132.58142657419</v>
+        <v>16992.24704921602</v>
       </c>
       <c r="D12">
-        <v>16230.77142657419</v>
+        <v>16282.14604921602</v>
       </c>
       <c r="E12">
-        <v>-3995.51</v>
+        <v>-3803.801</v>
       </c>
       <c r="F12">
-        <v>1917.09</v>
+        <v>2108.799</v>
       </c>
       <c r="G12">
         <v>2818.9</v>
@@ -2405,28 +2405,28 @@
         <v>10511.5</v>
       </c>
       <c r="M12">
-        <v>96.429627</v>
+        <v>106.0725897</v>
       </c>
       <c r="N12">
-        <v>10415.070373</v>
+        <v>10405.4274103</v>
       </c>
       <c r="O12">
-        <v>1978.86337087</v>
+        <v>1977.031207957</v>
       </c>
       <c r="P12">
-        <v>8436.207002130001</v>
+        <v>8428.396202343001</v>
       </c>
       <c r="Q12">
-        <v>8820.707002130001</v>
+        <v>8812.896202343001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09336916502551018</v>
+        <v>0.09381048291565511</v>
       </c>
       <c r="T12">
-        <v>0.8712459630429499</v>
+        <v>0.8793288551853955</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>109.0069548853487</v>
+        <v>99.09723171395335</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08797305979493306</v>
+        <v>0.08783957106690693</v>
       </c>
       <c r="C13">
-        <v>16992.24704921602</v>
+        <v>16852.23893270473</v>
       </c>
       <c r="D13">
-        <v>16282.14604921602</v>
+        <v>16333.84693270473</v>
       </c>
       <c r="E13">
-        <v>-3803.801</v>
+        <v>-3612.092</v>
       </c>
       <c r="F13">
-        <v>2108.799</v>
+        <v>2300.508</v>
       </c>
       <c r="G13">
         <v>2818.9</v>
@@ -2487,28 +2487,28 @@
         <v>10511.5</v>
       </c>
       <c r="M13">
-        <v>106.0725897</v>
+        <v>115.7155524</v>
       </c>
       <c r="N13">
-        <v>10405.4274103</v>
+        <v>10395.7844476</v>
       </c>
       <c r="O13">
-        <v>1977.031207957</v>
+        <v>1975.199045044</v>
       </c>
       <c r="P13">
-        <v>8428.396202343001</v>
+        <v>8420.585402556</v>
       </c>
       <c r="Q13">
-        <v>8812.896202343001</v>
+        <v>8805.085402556</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09381048291565511</v>
+        <v>0.09426183075784877</v>
       </c>
       <c r="T13">
-        <v>0.8793288551853955</v>
+        <v>0.8875954494219876</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>99.09723171395335</v>
+        <v>90.83912907112388</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08783957106690693</v>
+        <v>0.08770608233888082</v>
       </c>
       <c r="C14">
-        <v>16852.23893270473</v>
+        <v>16712.56019487975</v>
       </c>
       <c r="D14">
-        <v>16333.84693270473</v>
+        <v>16385.87719487975</v>
       </c>
       <c r="E14">
-        <v>-3612.092</v>
+        <v>-3420.383</v>
       </c>
       <c r="F14">
-        <v>2300.508</v>
+        <v>2492.217</v>
       </c>
       <c r="G14">
         <v>2818.9</v>
@@ -2569,28 +2569,28 @@
         <v>10511.5</v>
       </c>
       <c r="M14">
-        <v>115.7155524</v>
+        <v>125.3585151</v>
       </c>
       <c r="N14">
-        <v>10395.7844476</v>
+        <v>10386.1414849</v>
       </c>
       <c r="O14">
-        <v>1975.199045044</v>
+        <v>1973.366882131</v>
       </c>
       <c r="P14">
-        <v>8420.585402556</v>
+        <v>8412.774602768999</v>
       </c>
       <c r="Q14">
-        <v>8805.085402556</v>
+        <v>8797.274602768999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09426183075784877</v>
+        <v>0.09472355441250668</v>
       </c>
       <c r="T14">
-        <v>0.8875954494219876</v>
+        <v>0.8960520803076969</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>90.83912907112388</v>
+        <v>83.8515037579605</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08770608233888082</v>
+        <v>0.08757259361085469</v>
       </c>
       <c r="C15">
-        <v>16712.56019487975</v>
+        <v>16573.21399343407</v>
       </c>
       <c r="D15">
-        <v>16385.87719487975</v>
+        <v>16438.23999343407</v>
       </c>
       <c r="E15">
-        <v>-3420.383</v>
+        <v>-3228.674</v>
       </c>
       <c r="F15">
-        <v>2492.217</v>
+        <v>2683.926</v>
       </c>
       <c r="G15">
         <v>2818.9</v>
@@ -2651,28 +2651,28 @@
         <v>10511.5</v>
       </c>
       <c r="M15">
-        <v>125.3585151</v>
+        <v>135.0014778</v>
       </c>
       <c r="N15">
-        <v>10386.1414849</v>
+        <v>10376.4985222</v>
       </c>
       <c r="O15">
-        <v>1973.366882131</v>
+        <v>1971.534719218</v>
       </c>
       <c r="P15">
-        <v>8412.774602768999</v>
+        <v>8404.963802982</v>
       </c>
       <c r="Q15">
-        <v>8797.274602768999</v>
+        <v>8789.463802982</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09472355441250668</v>
+        <v>0.09519601582657522</v>
       </c>
       <c r="T15">
-        <v>0.8960520803076969</v>
+        <v>0.9047053770279576</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>83.8515037579605</v>
+        <v>77.8621106323919</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08757259361085469</v>
+        <v>0.08743910488282859</v>
       </c>
       <c r="C16">
-        <v>16573.21399343407</v>
+        <v>16434.20352655302</v>
       </c>
       <c r="D16">
-        <v>16438.23999343407</v>
+        <v>16490.93852655303</v>
       </c>
       <c r="E16">
-        <v>-3228.674</v>
+        <v>-3036.965</v>
       </c>
       <c r="F16">
-        <v>2683.926</v>
+        <v>2875.635000000001</v>
       </c>
       <c r="G16">
         <v>2818.9</v>
@@ -2733,28 +2733,28 @@
         <v>10511.5</v>
       </c>
       <c r="M16">
-        <v>135.0014778</v>
+        <v>144.6444405</v>
       </c>
       <c r="N16">
-        <v>10376.4985222</v>
+        <v>10366.8555595</v>
       </c>
       <c r="O16">
-        <v>1971.534719218</v>
+        <v>1969.702556305</v>
       </c>
       <c r="P16">
-        <v>8404.963802982</v>
+        <v>8397.153003195001</v>
       </c>
       <c r="Q16">
-        <v>8789.463802982</v>
+        <v>8781.653003195001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09519601582657522</v>
+        <v>0.09567959397979833</v>
       </c>
       <c r="T16">
-        <v>0.9047053770279576</v>
+        <v>0.9135622807298714</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>77.8621106323919</v>
+        <v>72.67130325689909</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08743910488282859</v>
+        <v>0.08730561615480245</v>
       </c>
       <c r="C17">
-        <v>16434.20352655303</v>
+        <v>16295.53203356549</v>
       </c>
       <c r="D17">
-        <v>16490.93852655303</v>
+        <v>16543.97603356549</v>
       </c>
       <c r="E17">
-        <v>-3036.965</v>
+        <v>-2845.256</v>
       </c>
       <c r="F17">
-        <v>2875.635</v>
+        <v>3067.344000000001</v>
       </c>
       <c r="G17">
         <v>2818.9</v>
@@ -2815,28 +2815,28 @@
         <v>10511.5</v>
       </c>
       <c r="M17">
-        <v>144.6444405</v>
+        <v>154.2874032</v>
       </c>
       <c r="N17">
-        <v>10366.8555595</v>
+        <v>10357.2125968</v>
       </c>
       <c r="O17">
-        <v>1969.702556305</v>
+        <v>1967.870393392</v>
       </c>
       <c r="P17">
-        <v>8397.153003195001</v>
+        <v>8389.342203407999</v>
       </c>
       <c r="Q17">
-        <v>8781.653003195001</v>
+        <v>8773.842203407999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09567959397979833</v>
+        <v>0.09617468589857435</v>
       </c>
       <c r="T17">
-        <v>0.9135622807298714</v>
+        <v>0.9226300630913545</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>72.67130325689911</v>
+        <v>68.12934680334291</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08730561615480245</v>
+        <v>0.08717212742677634</v>
       </c>
       <c r="C18">
-        <v>16295.53203356549</v>
+        <v>16157.20279560755</v>
       </c>
       <c r="D18">
-        <v>16543.97603356549</v>
+        <v>16597.35579560755</v>
       </c>
       <c r="E18">
-        <v>-2845.256</v>
+        <v>-2653.547</v>
       </c>
       <c r="F18">
-        <v>3067.344000000001</v>
+        <v>3259.053</v>
       </c>
       <c r="G18">
         <v>2818.9</v>
@@ -2897,28 +2897,28 @@
         <v>10511.5</v>
       </c>
       <c r="M18">
-        <v>154.2874032</v>
+        <v>163.9303659</v>
       </c>
       <c r="N18">
-        <v>10357.2125968</v>
+        <v>10347.5696341</v>
       </c>
       <c r="O18">
-        <v>1967.870393392</v>
+        <v>1966.038230479</v>
       </c>
       <c r="P18">
-        <v>8389.342203407999</v>
+        <v>8381.531403621</v>
       </c>
       <c r="Q18">
-        <v>8773.842203407999</v>
+        <v>8766.031403621</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09617468589857435</v>
+        <v>0.09668170774310403</v>
       </c>
       <c r="T18">
-        <v>0.9226300630913545</v>
+        <v>0.9319163462326325</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>68.12934680334291</v>
+        <v>64.12173816785216</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08717212742677634</v>
+        <v>0.08703863869875023</v>
       </c>
       <c r="C19">
-        <v>16157.20279560755</v>
+        <v>16019.21913629925</v>
       </c>
       <c r="D19">
-        <v>16597.35579560755</v>
+        <v>16651.08113629925</v>
       </c>
       <c r="E19">
-        <v>-2653.547</v>
+        <v>-2461.838</v>
       </c>
       <c r="F19">
-        <v>3259.053</v>
+        <v>3450.762000000001</v>
       </c>
       <c r="G19">
         <v>2818.9</v>
@@ -2979,28 +2979,28 @@
         <v>10511.5</v>
       </c>
       <c r="M19">
-        <v>163.9303659</v>
+        <v>173.5733286</v>
       </c>
       <c r="N19">
-        <v>10347.5696341</v>
+        <v>10337.9266714</v>
       </c>
       <c r="O19">
-        <v>1966.038230479</v>
+        <v>1964.206067566</v>
       </c>
       <c r="P19">
-        <v>8381.531403621</v>
+        <v>8373.720603834001</v>
       </c>
       <c r="Q19">
-        <v>8766.031403621</v>
+        <v>8758.220603834001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09668170774310403</v>
+        <v>0.09720109597408563</v>
       </c>
       <c r="T19">
-        <v>0.9319163462326325</v>
+        <v>0.9414291240846732</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>64.12173816785216</v>
+        <v>60.55941938074925</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08703863869875023</v>
+        <v>0.0869051499707241</v>
       </c>
       <c r="C20">
-        <v>16019.21913629925</v>
+        <v>15881.58442243438</v>
       </c>
       <c r="D20">
-        <v>16651.08113629925</v>
+        <v>16705.15542243438</v>
       </c>
       <c r="E20">
-        <v>-2461.838</v>
+        <v>-2270.129</v>
       </c>
       <c r="F20">
-        <v>3450.762</v>
+        <v>3642.471</v>
       </c>
       <c r="G20">
         <v>2818.9</v>
@@ -3061,28 +3061,28 @@
         <v>10511.5</v>
       </c>
       <c r="M20">
-        <v>173.5733286</v>
+        <v>183.2162913</v>
       </c>
       <c r="N20">
-        <v>10337.9266714</v>
+        <v>10328.2837087</v>
       </c>
       <c r="O20">
-        <v>1964.206067566</v>
+        <v>1962.373904653</v>
       </c>
       <c r="P20">
-        <v>8373.720603834001</v>
+        <v>8365.909804047</v>
       </c>
       <c r="Q20">
-        <v>8758.220603834001</v>
+        <v>8750.409804047</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09720109597408563</v>
+        <v>0.09773330860583221</v>
       </c>
       <c r="T20">
-        <v>0.9414291240846732</v>
+        <v>0.9511767853404681</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>60.55941938074926</v>
+        <v>57.37208151860456</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0869051499707241</v>
+        <v>0.08677166124269799</v>
       </c>
       <c r="C21">
-        <v>15881.58442243438</v>
+        <v>15744.30206468377</v>
       </c>
       <c r="D21">
-        <v>16705.15542243438</v>
+        <v>16759.58206468377</v>
       </c>
       <c r="E21">
-        <v>-2270.129</v>
+        <v>-2078.42</v>
       </c>
       <c r="F21">
-        <v>3642.471</v>
+        <v>3834.18</v>
       </c>
       <c r="G21">
         <v>2818.9</v>
@@ -3143,28 +3143,28 @@
         <v>10511.5</v>
       </c>
       <c r="M21">
-        <v>183.2162913</v>
+        <v>192.859254</v>
       </c>
       <c r="N21">
-        <v>10328.2837087</v>
+        <v>10318.640746</v>
       </c>
       <c r="O21">
-        <v>1962.373904653</v>
+        <v>1960.54174174</v>
       </c>
       <c r="P21">
-        <v>8365.909804047</v>
+        <v>8358.099004259999</v>
       </c>
       <c r="Q21">
-        <v>8750.409804047</v>
+        <v>8742.599004259999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09773330860583221</v>
+        <v>0.09827882655337247</v>
       </c>
       <c r="T21">
-        <v>0.9511767853404681</v>
+        <v>0.9611681381276581</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>57.37208151860456</v>
+        <v>54.50347744267433</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08677166124269799</v>
+        <v>0.08663817251467186</v>
       </c>
       <c r="C22">
-        <v>15744.30206468377</v>
+        <v>15607.37551831242</v>
       </c>
       <c r="D22">
-        <v>16759.58206468377</v>
+        <v>16814.36451831242</v>
       </c>
       <c r="E22">
-        <v>-2078.42</v>
+        <v>-1886.711</v>
       </c>
       <c r="F22">
-        <v>3834.18</v>
+        <v>4025.889000000001</v>
       </c>
       <c r="G22">
         <v>2818.9</v>
@@ -3225,28 +3225,28 @@
         <v>10511.5</v>
       </c>
       <c r="M22">
-        <v>192.859254</v>
+        <v>202.5022167</v>
       </c>
       <c r="N22">
-        <v>10318.640746</v>
+        <v>10308.9977833</v>
       </c>
       <c r="O22">
-        <v>1960.54174174</v>
+        <v>1958.709578827</v>
       </c>
       <c r="P22">
-        <v>8358.099004259999</v>
+        <v>8350.288204472999</v>
       </c>
       <c r="Q22">
-        <v>8742.599004259999</v>
+        <v>8734.788204472999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09827882655337247</v>
+        <v>0.09883815508186311</v>
       </c>
       <c r="T22">
-        <v>0.9611681381276581</v>
+        <v>0.9714124365550298</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>54.50347744267433</v>
+        <v>51.90807375492793</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08663817251467185</v>
+        <v>0.08650468378664575</v>
       </c>
       <c r="C23">
-        <v>15607.37551831243</v>
+        <v>15470.80828391075</v>
       </c>
       <c r="D23">
-        <v>16814.36451831243</v>
+        <v>16869.50628391074</v>
       </c>
       <c r="E23">
-        <v>-1886.711</v>
+        <v>-1695.002</v>
       </c>
       <c r="F23">
-        <v>4025.889</v>
+        <v>4217.598</v>
       </c>
       <c r="G23">
         <v>2818.9</v>
@@ -3307,28 +3307,28 @@
         <v>10511.5</v>
       </c>
       <c r="M23">
-        <v>202.5022167</v>
+        <v>212.1451794</v>
       </c>
       <c r="N23">
-        <v>10308.9977833</v>
+        <v>10299.3548206</v>
       </c>
       <c r="O23">
-        <v>1958.709578827</v>
+        <v>1956.877415914</v>
       </c>
       <c r="P23">
-        <v>8350.288204472999</v>
+        <v>8342.477404686</v>
       </c>
       <c r="Q23">
-        <v>8734.788204472999</v>
+        <v>8726.977404686</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09883815508186311</v>
+        <v>0.09941182536749454</v>
       </c>
       <c r="T23">
-        <v>0.9714124365550298</v>
+        <v>0.9819194093010521</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>51.90807375492794</v>
+        <v>49.54861585697667</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08650468378664575</v>
+        <v>0.08637119505861963</v>
       </c>
       <c r="C24">
-        <v>15470.80828391075</v>
+        <v>15334.60390814018</v>
       </c>
       <c r="D24">
-        <v>16869.50628391074</v>
+        <v>16925.01090814018</v>
       </c>
       <c r="E24">
-        <v>-1695.002</v>
+        <v>-1503.293</v>
       </c>
       <c r="F24">
-        <v>4217.598</v>
+        <v>4409.307000000001</v>
       </c>
       <c r="G24">
         <v>2818.9</v>
@@ -3389,28 +3389,28 @@
         <v>10511.5</v>
       </c>
       <c r="M24">
-        <v>212.1451794</v>
+        <v>221.7881421</v>
       </c>
       <c r="N24">
-        <v>10299.3548206</v>
+        <v>10289.7118579</v>
       </c>
       <c r="O24">
-        <v>1956.877415914</v>
+        <v>1955.045253001</v>
       </c>
       <c r="P24">
-        <v>8342.477404686</v>
+        <v>8334.666604898999</v>
       </c>
       <c r="Q24">
-        <v>8726.977404686</v>
+        <v>8719.166604898999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09941182536749454</v>
+        <v>0.1000003961800255</v>
       </c>
       <c r="T24">
-        <v>0.9819194093010521</v>
+        <v>0.9926992904300881</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>49.54861585697667</v>
+        <v>47.39432821102115</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08637119505861963</v>
+        <v>0.08623770633059352</v>
       </c>
       <c r="C25">
-        <v>15334.60390814018</v>
+        <v>15198.76598449365</v>
       </c>
       <c r="D25">
-        <v>16925.01090814018</v>
+        <v>16980.88198449365</v>
       </c>
       <c r="E25">
-        <v>-1503.293</v>
+        <v>-1311.584</v>
       </c>
       <c r="F25">
-        <v>4409.307000000001</v>
+        <v>4601.016000000001</v>
       </c>
       <c r="G25">
         <v>2818.9</v>
@@ -3471,28 +3471,28 @@
         <v>10511.5</v>
       </c>
       <c r="M25">
-        <v>221.7881421</v>
+        <v>231.4311048</v>
       </c>
       <c r="N25">
-        <v>10289.7118579</v>
+        <v>10280.0688952</v>
       </c>
       <c r="O25">
-        <v>1955.045253001</v>
+        <v>1953.213090088</v>
       </c>
       <c r="P25">
-        <v>8334.666604898999</v>
+        <v>8326.855805112</v>
       </c>
       <c r="Q25">
-        <v>8719.166604898999</v>
+        <v>8711.355805112</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1000003961800255</v>
+        <v>0.1006044556981494</v>
       </c>
       <c r="T25">
-        <v>0.9926992904300881</v>
+        <v>1.003762852641467</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>47.39432821102115</v>
+        <v>45.41956453556195</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08623770633059352</v>
+        <v>0.08610421760256737</v>
       </c>
       <c r="C26">
-        <v>15198.76598449365</v>
+        <v>15063.2981540711</v>
       </c>
       <c r="D26">
-        <v>16980.88198449365</v>
+        <v>17037.12315407109</v>
       </c>
       <c r="E26">
-        <v>-1311.584</v>
+        <v>-1119.875</v>
       </c>
       <c r="F26">
-        <v>4601.016000000001</v>
+        <v>4792.725</v>
       </c>
       <c r="G26">
         <v>2818.9</v>
@@ -3553,28 +3553,28 @@
         <v>10511.5</v>
       </c>
       <c r="M26">
-        <v>231.4311048</v>
+        <v>241.0740675</v>
       </c>
       <c r="N26">
-        <v>10280.0688952</v>
+        <v>10270.4259325</v>
       </c>
       <c r="O26">
-        <v>1953.213090088</v>
+        <v>1951.380927175</v>
       </c>
       <c r="P26">
-        <v>8326.855805112</v>
+        <v>8319.045005325001</v>
       </c>
       <c r="Q26">
-        <v>8711.355805112</v>
+        <v>8703.545005325001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1006044556981494</v>
+        <v>0.1012246234700898</v>
       </c>
       <c r="T26">
-        <v>1.003762852641467</v>
+        <v>1.015121443178483</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>45.41956453556195</v>
+        <v>43.60278195413947</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08610421760256737</v>
+        <v>0.08597072887454127</v>
       </c>
       <c r="C27">
-        <v>15063.2981540711</v>
+        <v>14928.20410637041</v>
       </c>
       <c r="D27">
-        <v>17037.12315407109</v>
+        <v>17093.73810637041</v>
       </c>
       <c r="E27">
-        <v>-1119.875</v>
+        <v>-928.1660000000002</v>
       </c>
       <c r="F27">
-        <v>4792.725</v>
+        <v>4984.434</v>
       </c>
       <c r="G27">
         <v>2818.9</v>
@@ -3635,28 +3635,28 @@
         <v>10511.5</v>
       </c>
       <c r="M27">
-        <v>241.0740675</v>
+        <v>250.7170302</v>
       </c>
       <c r="N27">
-        <v>10270.4259325</v>
+        <v>10260.7829698</v>
       </c>
       <c r="O27">
-        <v>1951.380927175</v>
+        <v>1949.548764262</v>
       </c>
       <c r="P27">
-        <v>8319.045005325001</v>
+        <v>8311.234205538</v>
       </c>
       <c r="Q27">
-        <v>8703.545005325001</v>
+        <v>8695.734205538</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1012246234700898</v>
+        <v>0.1018615525331639</v>
       </c>
       <c r="T27">
-        <v>1.015121443178483</v>
+        <v>1.026787022648932</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>43.60278195413947</v>
+        <v>41.92575187898026</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08597072887454127</v>
+        <v>0.08583724014651514</v>
       </c>
       <c r="C28">
-        <v>14928.20410637041</v>
+        <v>14793.4875800944</v>
       </c>
       <c r="D28">
-        <v>17093.73810637041</v>
+        <v>17150.73058009439</v>
       </c>
       <c r="E28">
-        <v>-928.1660000000002</v>
+        <v>-736.4569999999994</v>
       </c>
       <c r="F28">
-        <v>4984.434</v>
+        <v>5176.143000000001</v>
       </c>
       <c r="G28">
         <v>2818.9</v>
@@ -3717,28 +3717,28 @@
         <v>10511.5</v>
       </c>
       <c r="M28">
-        <v>250.7170302</v>
+        <v>260.3599929</v>
       </c>
       <c r="N28">
-        <v>10260.7829698</v>
+        <v>10251.1400071</v>
       </c>
       <c r="O28">
-        <v>1949.548764262</v>
+        <v>1947.716601349</v>
       </c>
       <c r="P28">
-        <v>8311.234205538</v>
+        <v>8303.423405751</v>
       </c>
       <c r="Q28">
-        <v>8695.734205538</v>
+        <v>8687.923405751</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1018615525331639</v>
+        <v>0.102515931707555</v>
       </c>
       <c r="T28">
-        <v>1.026787022648932</v>
+        <v>1.038772207036379</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>41.92575187898026</v>
+        <v>40.37294625383284</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08583724014651514</v>
+        <v>0.08570375141848902</v>
       </c>
       <c r="C29">
-        <v>14793.4875800944</v>
+        <v>14659.15236397364</v>
       </c>
       <c r="D29">
-        <v>17150.73058009439</v>
+        <v>17208.10436397364</v>
       </c>
       <c r="E29">
-        <v>-736.4569999999994</v>
+        <v>-544.7479999999996</v>
       </c>
       <c r="F29">
-        <v>5176.143000000001</v>
+        <v>5367.852000000001</v>
       </c>
       <c r="G29">
         <v>2818.9</v>
@@ -3799,28 +3799,28 @@
         <v>10511.5</v>
       </c>
       <c r="M29">
-        <v>260.3599929</v>
+        <v>270.0029556</v>
       </c>
       <c r="N29">
-        <v>10251.1400071</v>
+        <v>10241.4970444</v>
       </c>
       <c r="O29">
-        <v>1947.716601349</v>
+        <v>1945.884438436</v>
       </c>
       <c r="P29">
-        <v>8303.423405751</v>
+        <v>8295.612605963999</v>
       </c>
       <c r="Q29">
-        <v>8687.923405751</v>
+        <v>8680.112605963999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.102515931707555</v>
+        <v>0.1031884880812348</v>
       </c>
       <c r="T29">
-        <v>1.038772207036379</v>
+        <v>1.051090313212366</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>40.37294625383284</v>
+        <v>38.93105531619595</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08570375141848902</v>
+        <v>0.08557026269046292</v>
       </c>
       <c r="C30">
-        <v>14659.15236397364</v>
+        <v>14525.20229760619</v>
       </c>
       <c r="D30">
-        <v>17208.10436397364</v>
+        <v>17265.86329760619</v>
       </c>
       <c r="E30">
-        <v>-544.7479999999996</v>
+        <v>-353.0389999999989</v>
       </c>
       <c r="F30">
-        <v>5367.852000000001</v>
+        <v>5559.561000000002</v>
       </c>
       <c r="G30">
         <v>2818.9</v>
@@ -3881,28 +3881,28 @@
         <v>10511.5</v>
       </c>
       <c r="M30">
-        <v>270.0029556</v>
+        <v>279.6459183000001</v>
       </c>
       <c r="N30">
-        <v>10241.4970444</v>
+        <v>10231.8540817</v>
       </c>
       <c r="O30">
-        <v>1945.884438436</v>
+        <v>1944.052275523</v>
       </c>
       <c r="P30">
-        <v>8295.612605963999</v>
+        <v>8287.801806177</v>
       </c>
       <c r="Q30">
-        <v>8680.112605963999</v>
+        <v>8672.301806177</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1031884880812348</v>
+        <v>0.1038799897048774</v>
       </c>
       <c r="T30">
-        <v>1.051090313212366</v>
+        <v>1.06375540829472</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>38.93105531619595</v>
+        <v>37.58860513287884</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08557026269046289</v>
+        <v>0.08543677396243679</v>
       </c>
       <c r="C31">
-        <v>14525.2022976062</v>
+        <v>14391.64127231408</v>
       </c>
       <c r="D31">
-        <v>17265.8632976062</v>
+        <v>17324.01127231408</v>
       </c>
       <c r="E31">
-        <v>-353.0390000000007</v>
+        <v>-161.3299999999999</v>
       </c>
       <c r="F31">
-        <v>5559.561</v>
+        <v>5751.27</v>
       </c>
       <c r="G31">
         <v>2818.9</v>
@@ -3963,28 +3963,28 @@
         <v>10511.5</v>
       </c>
       <c r="M31">
-        <v>279.6459182999999</v>
+        <v>289.288881</v>
       </c>
       <c r="N31">
-        <v>10231.8540817</v>
+        <v>10222.211119</v>
       </c>
       <c r="O31">
-        <v>1944.052275523</v>
+        <v>1942.22011261</v>
       </c>
       <c r="P31">
-        <v>8287.801806177</v>
+        <v>8279.991006389999</v>
       </c>
       <c r="Q31">
-        <v>8672.301806177</v>
+        <v>8664.491006389999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1038799897048773</v>
+        <v>0.1045912485177669</v>
       </c>
       <c r="T31">
-        <v>1.063755408294719</v>
+        <v>1.076782363236569</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>37.58860513287885</v>
+        <v>36.33565162844955</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08543677396243679</v>
+        <v>0.08530328523441066</v>
       </c>
       <c r="C32">
-        <v>14391.64127231408</v>
+        <v>14258.47323201728</v>
       </c>
       <c r="D32">
-        <v>17324.01127231408</v>
+        <v>17382.55223201727</v>
       </c>
       <c r="E32">
-        <v>-161.3299999999999</v>
+        <v>30.37899999999991</v>
       </c>
       <c r="F32">
-        <v>5751.27</v>
+        <v>5942.979</v>
       </c>
       <c r="G32">
         <v>2818.9</v>
@@ -4045,28 +4045,28 @@
         <v>10511.5</v>
       </c>
       <c r="M32">
-        <v>289.288881</v>
+        <v>298.9318437</v>
       </c>
       <c r="N32">
-        <v>10222.211119</v>
+        <v>10212.5681563</v>
       </c>
       <c r="O32">
-        <v>1942.22011261</v>
+        <v>1940.387949697</v>
       </c>
       <c r="P32">
-        <v>8279.991006389999</v>
+        <v>8272.180206603</v>
       </c>
       <c r="Q32">
-        <v>8664.491006389999</v>
+        <v>8656.680206603</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1045912485177669</v>
+        <v>0.1053231235281314</v>
       </c>
       <c r="T32">
-        <v>1.076782363236569</v>
+        <v>1.090186911075283</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>36.33565162844955</v>
+        <v>35.16353383398344</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08530328523441066</v>
+        <v>0.08516979650638454</v>
       </c>
       <c r="C33">
-        <v>14258.47323201728</v>
+        <v>14125.70217412534</v>
       </c>
       <c r="D33">
-        <v>17382.55223201727</v>
+        <v>17441.49017412535</v>
       </c>
       <c r="E33">
-        <v>30.37899999999991</v>
+        <v>222.0880000000006</v>
       </c>
       <c r="F33">
-        <v>5942.979</v>
+        <v>6134.688000000001</v>
       </c>
       <c r="G33">
         <v>2818.9</v>
@@ -4127,28 +4127,28 @@
         <v>10511.5</v>
       </c>
       <c r="M33">
-        <v>298.9318437</v>
+        <v>308.5748064000001</v>
       </c>
       <c r="N33">
-        <v>10212.5681563</v>
+        <v>10202.9251936</v>
       </c>
       <c r="O33">
-        <v>1940.387949697</v>
+        <v>1938.555786784</v>
       </c>
       <c r="P33">
-        <v>8272.180206603</v>
+        <v>8264.369406816</v>
       </c>
       <c r="Q33">
-        <v>8656.680206603</v>
+        <v>8648.869406816</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1053231235281314</v>
+        <v>0.1060765242740949</v>
       </c>
       <c r="T33">
-        <v>1.090186911075283</v>
+        <v>1.103985710321018</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>35.16353383398344</v>
+        <v>34.06467340167146</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08516979650638454</v>
+        <v>0.08503630777835842</v>
       </c>
       <c r="C34">
-        <v>14125.70217412534</v>
+        <v>13993.33215044738</v>
       </c>
       <c r="D34">
-        <v>17441.49017412535</v>
+        <v>17500.82915044737</v>
       </c>
       <c r="E34">
-        <v>222.0880000000006</v>
+        <v>413.7970000000005</v>
       </c>
       <c r="F34">
-        <v>6134.688000000001</v>
+        <v>6326.397000000001</v>
       </c>
       <c r="G34">
         <v>2818.9</v>
@@ -4209,28 +4209,28 @@
         <v>10511.5</v>
       </c>
       <c r="M34">
-        <v>308.5748064000001</v>
+        <v>318.2177691</v>
       </c>
       <c r="N34">
-        <v>10202.9251936</v>
+        <v>10193.2822309</v>
       </c>
       <c r="O34">
-        <v>1938.555786784</v>
+        <v>1936.723623871</v>
       </c>
       <c r="P34">
-        <v>8264.369406816</v>
+        <v>8256.558607029001</v>
       </c>
       <c r="Q34">
-        <v>8648.869406816</v>
+        <v>8641.058607029001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1060765242740949</v>
+        <v>0.1068524145945648</v>
       </c>
       <c r="T34">
-        <v>1.103985710321018</v>
+        <v>1.11819641402185</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>34.06467340167146</v>
+        <v>33.03241057131778</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08503630777835842</v>
+        <v>0.08490281905033231</v>
       </c>
       <c r="C35">
-        <v>13993.33215044738</v>
+        <v>13861.36726812054</v>
       </c>
       <c r="D35">
-        <v>17500.82915044737</v>
+        <v>17560.57326812054</v>
       </c>
       <c r="E35">
-        <v>413.7970000000005</v>
+        <v>605.5060000000003</v>
       </c>
       <c r="F35">
-        <v>6326.397000000001</v>
+        <v>6518.106000000001</v>
       </c>
       <c r="G35">
         <v>2818.9</v>
@@ -4291,28 +4291,28 @@
         <v>10511.5</v>
       </c>
       <c r="M35">
-        <v>318.2177691</v>
+        <v>327.8607318</v>
       </c>
       <c r="N35">
-        <v>10193.2822309</v>
+        <v>10183.6392682</v>
       </c>
       <c r="O35">
-        <v>1936.723623871</v>
+        <v>1934.891460958</v>
       </c>
       <c r="P35">
-        <v>8256.558607029001</v>
+        <v>8248.747807242</v>
       </c>
       <c r="Q35">
-        <v>8641.058607029001</v>
+        <v>8633.247807242</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1068524145945648</v>
+        <v>0.1076518167429278</v>
       </c>
       <c r="T35">
-        <v>1.11819641402185</v>
+        <v>1.132837745107556</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>33.03241057131778</v>
+        <v>32.06086908392608</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08490281905033231</v>
+        <v>0.08476933032230617</v>
       </c>
       <c r="C36">
-        <v>13861.36726812054</v>
+        <v>13729.81169055771</v>
       </c>
       <c r="D36">
-        <v>17560.57326812054</v>
+        <v>17620.72669055771</v>
       </c>
       <c r="E36">
-        <v>605.5060000000003</v>
+        <v>797.2150000000011</v>
       </c>
       <c r="F36">
-        <v>6518.106000000001</v>
+        <v>6709.815000000001</v>
       </c>
       <c r="G36">
         <v>2818.9</v>
@@ -4373,28 +4373,28 @@
         <v>10511.5</v>
       </c>
       <c r="M36">
-        <v>327.8607318</v>
+        <v>337.5036945000001</v>
       </c>
       <c r="N36">
-        <v>10183.6392682</v>
+        <v>10173.9963055</v>
       </c>
       <c r="O36">
-        <v>1934.891460958</v>
+        <v>1933.059298045</v>
       </c>
       <c r="P36">
-        <v>8248.747807242</v>
+        <v>8240.937007455001</v>
       </c>
       <c r="Q36">
-        <v>8633.247807242</v>
+        <v>8625.437007455001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1076518167429278</v>
+        <v>0.1084758158804711</v>
       </c>
       <c r="T36">
-        <v>1.132837745107556</v>
+        <v>1.147929578688206</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>32.06086908392608</v>
+        <v>31.14484425295676</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08476933032230617</v>
+        <v>0.08463584159428007</v>
       </c>
       <c r="C37">
-        <v>13729.81169055771</v>
+        <v>13598.66963841457</v>
       </c>
       <c r="D37">
-        <v>17620.72669055771</v>
+        <v>17681.29363841457</v>
       </c>
       <c r="E37">
-        <v>797.2150000000011</v>
+        <v>988.9240000000009</v>
       </c>
       <c r="F37">
-        <v>6709.815000000001</v>
+        <v>6901.524000000001</v>
       </c>
       <c r="G37">
         <v>2818.9</v>
@@ -4455,28 +4455,28 @@
         <v>10511.5</v>
       </c>
       <c r="M37">
-        <v>337.5036945000001</v>
+        <v>347.1466572</v>
       </c>
       <c r="N37">
-        <v>10173.9963055</v>
+        <v>10164.3533428</v>
       </c>
       <c r="O37">
-        <v>1933.059298045</v>
+        <v>1931.227135132</v>
       </c>
       <c r="P37">
-        <v>8240.937007455001</v>
+        <v>8233.126207668</v>
       </c>
       <c r="Q37">
-        <v>8625.437007455001</v>
+        <v>8617.626207668</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1084758158804711</v>
+        <v>0.1093255649910626</v>
       </c>
       <c r="T37">
-        <v>1.147929578688206</v>
+        <v>1.163493032068251</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>31.14484425295676</v>
+        <v>30.27970969037462</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08463584159428009</v>
+        <v>0.08450235286625397</v>
       </c>
       <c r="C38">
-        <v>13598.66963841457</v>
+        <v>13467.94539057691</v>
       </c>
       <c r="D38">
-        <v>17681.29363841457</v>
+        <v>17742.27839057691</v>
       </c>
       <c r="E38">
-        <v>988.924</v>
+        <v>1180.633</v>
       </c>
       <c r="F38">
-        <v>6901.524</v>
+        <v>7093.233</v>
       </c>
       <c r="G38">
         <v>2818.9</v>
@@ -4537,28 +4537,28 @@
         <v>10511.5</v>
       </c>
       <c r="M38">
-        <v>347.1466572</v>
+        <v>356.7896199</v>
       </c>
       <c r="N38">
-        <v>10164.3533428</v>
+        <v>10154.7103801</v>
       </c>
       <c r="O38">
-        <v>1931.227135132</v>
+        <v>1929.394972219</v>
       </c>
       <c r="P38">
-        <v>8233.126207668</v>
+        <v>8225.315407881</v>
       </c>
       <c r="Q38">
-        <v>8617.626207668</v>
+        <v>8609.815407881</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1093255649910626</v>
+        <v>0.1102022902638952</v>
       </c>
       <c r="T38">
-        <v>1.163493032068251</v>
+        <v>1.179550563333378</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>30.27970969037463</v>
+        <v>29.46133915820234</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08450235286625397</v>
+        <v>0.08436886413822783</v>
       </c>
       <c r="C39">
-        <v>13467.94539057691</v>
+        <v>13337.64328516825</v>
       </c>
       <c r="D39">
-        <v>17742.27839057691</v>
+        <v>17803.68528516825</v>
       </c>
       <c r="E39">
-        <v>1180.633</v>
+        <v>1372.342000000001</v>
       </c>
       <c r="F39">
-        <v>7093.233</v>
+        <v>7284.942000000001</v>
       </c>
       <c r="G39">
         <v>2818.9</v>
@@ -4619,28 +4619,28 @@
         <v>10511.5</v>
       </c>
       <c r="M39">
-        <v>356.7896199</v>
+        <v>366.4325826</v>
       </c>
       <c r="N39">
-        <v>10154.7103801</v>
+        <v>10145.0674174</v>
       </c>
       <c r="O39">
-        <v>1929.394972219</v>
+        <v>1927.562809306</v>
       </c>
       <c r="P39">
-        <v>8225.315407881</v>
+        <v>8217.504608093999</v>
       </c>
       <c r="Q39">
-        <v>8609.815407881</v>
+        <v>8602.004608093999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1102022902638952</v>
+        <v>0.1111072969971417</v>
       </c>
       <c r="T39">
-        <v>1.179550563333378</v>
+        <v>1.196126079478024</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>29.46133915820234</v>
+        <v>28.68604075930228</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08436886413822783</v>
+        <v>0.08423537541020172</v>
       </c>
       <c r="C40">
-        <v>13337.64328516825</v>
+        <v>13207.76772057847</v>
       </c>
       <c r="D40">
-        <v>17803.68528516825</v>
+        <v>17865.51872057847</v>
       </c>
       <c r="E40">
-        <v>1372.342000000001</v>
+        <v>1564.051</v>
       </c>
       <c r="F40">
-        <v>7284.942000000001</v>
+        <v>7476.651000000001</v>
       </c>
       <c r="G40">
         <v>2818.9</v>
@@ -4701,28 +4701,28 @@
         <v>10511.5</v>
       </c>
       <c r="M40">
-        <v>366.4325826</v>
+        <v>376.0755453</v>
       </c>
       <c r="N40">
-        <v>10145.0674174</v>
+        <v>10135.4244547</v>
       </c>
       <c r="O40">
-        <v>1927.562809306</v>
+        <v>1925.730646393</v>
       </c>
       <c r="P40">
-        <v>8217.504608093999</v>
+        <v>8209.693808307</v>
       </c>
       <c r="Q40">
-        <v>8602.004608093999</v>
+        <v>8594.193808307</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1111072969971417</v>
+        <v>0.1120419760822979</v>
       </c>
       <c r="T40">
-        <v>1.196126079478024</v>
+        <v>1.213245055168397</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>28.68604075930228</v>
+        <v>27.9505012526535</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08423537541020172</v>
+        <v>0.08410188668217561</v>
       </c>
       <c r="C41">
-        <v>13207.76772057847</v>
+        <v>13078.32315651412</v>
       </c>
       <c r="D41">
-        <v>17865.51872057847</v>
+        <v>17927.78315651412</v>
       </c>
       <c r="E41">
-        <v>1564.051</v>
+        <v>1755.76</v>
       </c>
       <c r="F41">
-        <v>7476.651000000001</v>
+        <v>7668.360000000001</v>
       </c>
       <c r="G41">
         <v>2818.9</v>
@@ -4783,28 +4783,28 @@
         <v>10511.5</v>
       </c>
       <c r="M41">
-        <v>376.0755453</v>
+        <v>385.718508</v>
       </c>
       <c r="N41">
-        <v>10135.4244547</v>
+        <v>10125.781492</v>
       </c>
       <c r="O41">
-        <v>1925.730646393</v>
+        <v>1923.89848348</v>
       </c>
       <c r="P41">
-        <v>8209.693808307</v>
+        <v>8201.883008520001</v>
       </c>
       <c r="Q41">
-        <v>8594.193808307</v>
+        <v>8586.383008520001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1120419760822979</v>
+        <v>0.1130078111369593</v>
       </c>
       <c r="T41">
-        <v>1.213245055168397</v>
+        <v>1.230934663381782</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>27.9505012526535</v>
+        <v>27.25173872133717</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08410188668217561</v>
+        <v>0.08396839795414948</v>
       </c>
       <c r="C42">
-        <v>13078.32315651412</v>
+        <v>12949.31411507057</v>
       </c>
       <c r="D42">
-        <v>17927.78315651412</v>
+        <v>17990.48311507057</v>
       </c>
       <c r="E42">
-        <v>1755.76</v>
+        <v>1947.469000000001</v>
       </c>
       <c r="F42">
-        <v>7668.360000000001</v>
+        <v>7860.069000000001</v>
       </c>
       <c r="G42">
         <v>2818.9</v>
@@ -4865,28 +4865,28 @@
         <v>10511.5</v>
       </c>
       <c r="M42">
-        <v>385.718508</v>
+        <v>395.3614707</v>
       </c>
       <c r="N42">
-        <v>10125.781492</v>
+        <v>10116.1385293</v>
       </c>
       <c r="O42">
-        <v>1923.89848348</v>
+        <v>1922.066320567</v>
       </c>
       <c r="P42">
-        <v>8201.883008520001</v>
+        <v>8194.072208733</v>
       </c>
       <c r="Q42">
-        <v>8586.383008520001</v>
+        <v>8578.572208733</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1130078111369593</v>
+        <v>0.1140063863629652</v>
       </c>
       <c r="T42">
-        <v>1.230934663381782</v>
+        <v>1.249223919331214</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>27.25173872133717</v>
+        <v>26.58706216715821</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08396839795414948</v>
+        <v>0.08383490922612337</v>
       </c>
       <c r="C43">
-        <v>12949.31411507057</v>
+        <v>12820.74518182683</v>
       </c>
       <c r="D43">
-        <v>17990.48311507057</v>
+        <v>18053.62318182684</v>
       </c>
       <c r="E43">
-        <v>1947.469000000001</v>
+        <v>2139.178000000001</v>
       </c>
       <c r="F43">
-        <v>7860.069000000001</v>
+        <v>8051.778000000001</v>
       </c>
       <c r="G43">
         <v>2818.9</v>
@@ -4947,28 +4947,28 @@
         <v>10511.5</v>
       </c>
       <c r="M43">
-        <v>395.3614707</v>
+        <v>405.0044334</v>
       </c>
       <c r="N43">
-        <v>10116.1385293</v>
+        <v>10106.4955666</v>
       </c>
       <c r="O43">
-        <v>1922.066320567</v>
+        <v>1920.234157654</v>
       </c>
       <c r="P43">
-        <v>8194.072208733</v>
+        <v>8186.261408946</v>
       </c>
       <c r="Q43">
-        <v>8578.572208733</v>
+        <v>8570.761408946</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1140063863629652</v>
+        <v>0.1150393952174541</v>
       </c>
       <c r="T43">
-        <v>1.249223919331214</v>
+        <v>1.268143839278903</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>26.58706216715821</v>
+        <v>25.95403687746397</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08383490922612337</v>
+        <v>0.08370142049809726</v>
       </c>
       <c r="C44">
-        <v>12820.74518182684</v>
+        <v>12692.62100696356</v>
       </c>
       <c r="D44">
-        <v>18053.62318182684</v>
+        <v>18117.20800696356</v>
       </c>
       <c r="E44">
-        <v>2139.178</v>
+        <v>2330.887000000001</v>
       </c>
       <c r="F44">
-        <v>8051.778</v>
+        <v>8243.487000000001</v>
       </c>
       <c r="G44">
         <v>2818.9</v>
@@ -5029,28 +5029,28 @@
         <v>10511.5</v>
       </c>
       <c r="M44">
-        <v>405.0044334</v>
+        <v>414.6473961</v>
       </c>
       <c r="N44">
-        <v>10106.4955666</v>
+        <v>10096.8526039</v>
       </c>
       <c r="O44">
-        <v>1920.234157654</v>
+        <v>1918.401994741</v>
       </c>
       <c r="P44">
-        <v>8186.261408946</v>
+        <v>8178.450609159001</v>
       </c>
       <c r="Q44">
-        <v>8570.761408946</v>
+        <v>8562.950609159001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1150393952174541</v>
+        <v>0.1161086499966618</v>
       </c>
       <c r="T44">
-        <v>1.268143839278903</v>
+        <v>1.287727616066861</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>25.95403687746397</v>
+        <v>25.35045462449969</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08370142049809726</v>
+        <v>0.08356793177007113</v>
       </c>
       <c r="C45">
-        <v>12692.62100696356</v>
+        <v>12564.94630640462</v>
       </c>
       <c r="D45">
-        <v>18117.20800696356</v>
+        <v>18181.24230640462</v>
       </c>
       <c r="E45">
-        <v>2330.887000000001</v>
+        <v>2522.596</v>
       </c>
       <c r="F45">
-        <v>8243.487000000001</v>
+        <v>8435.196</v>
       </c>
       <c r="G45">
         <v>2818.9</v>
@@ -5111,28 +5111,28 @@
         <v>10511.5</v>
       </c>
       <c r="M45">
-        <v>414.6473961</v>
+        <v>424.2903588</v>
       </c>
       <c r="N45">
-        <v>10096.8526039</v>
+        <v>10087.2096412</v>
       </c>
       <c r="O45">
-        <v>1918.401994741</v>
+        <v>1916.569831828</v>
       </c>
       <c r="P45">
-        <v>8178.450609159001</v>
+        <v>8170.639809371999</v>
       </c>
       <c r="Q45">
-        <v>8562.950609159001</v>
+        <v>8555.139809371998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1161086499966618</v>
+        <v>0.1172160924465556</v>
       </c>
       <c r="T45">
-        <v>1.287727616066861</v>
+        <v>1.30801081345439</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>25.35045462449969</v>
+        <v>24.77430792848833</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08356793177007113</v>
+        <v>0.083434443042045</v>
       </c>
       <c r="C46">
-        <v>12564.94630640462</v>
+        <v>12437.7258629831</v>
       </c>
       <c r="D46">
-        <v>18181.24230640462</v>
+        <v>18245.7308629831</v>
       </c>
       <c r="E46">
-        <v>2522.596</v>
+        <v>2714.305</v>
       </c>
       <c r="F46">
-        <v>8435.196</v>
+        <v>8626.905000000001</v>
       </c>
       <c r="G46">
         <v>2818.9</v>
@@ -5193,28 +5193,28 @@
         <v>10511.5</v>
       </c>
       <c r="M46">
-        <v>424.2903588</v>
+        <v>433.9333215</v>
       </c>
       <c r="N46">
-        <v>10087.2096412</v>
+        <v>10077.5666785</v>
       </c>
       <c r="O46">
-        <v>1916.569831828</v>
+        <v>1914.737668915</v>
       </c>
       <c r="P46">
-        <v>8170.639809371999</v>
+        <v>8162.829009585</v>
       </c>
       <c r="Q46">
-        <v>8555.139809371998</v>
+        <v>8547.329009584999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1172160924465556</v>
+        <v>0.1183638055309909</v>
       </c>
       <c r="T46">
-        <v>1.30801081345439</v>
+        <v>1.329031581656009</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>24.77430792848833</v>
+        <v>24.2237677522997</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.083434443042045</v>
+        <v>0.0833009543140189</v>
       </c>
       <c r="C47">
-        <v>12437.7258629831</v>
+        <v>12310.96452763215</v>
       </c>
       <c r="D47">
-        <v>18245.7308629831</v>
+        <v>18310.67852763215</v>
       </c>
       <c r="E47">
-        <v>2714.305</v>
+        <v>2906.014000000001</v>
       </c>
       <c r="F47">
-        <v>8626.905000000001</v>
+        <v>8818.614000000001</v>
       </c>
       <c r="G47">
         <v>2818.9</v>
@@ -5275,28 +5275,28 @@
         <v>10511.5</v>
       </c>
       <c r="M47">
-        <v>433.9333215</v>
+        <v>443.5762842</v>
       </c>
       <c r="N47">
-        <v>10077.5666785</v>
+        <v>10067.9237158</v>
       </c>
       <c r="O47">
-        <v>1914.737668915</v>
+        <v>1912.905506002</v>
       </c>
       <c r="P47">
-        <v>8162.829009585</v>
+        <v>8155.018209798</v>
       </c>
       <c r="Q47">
-        <v>8547.329009584999</v>
+        <v>8539.518209798</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1183638055309909</v>
+        <v>0.1195540265074424</v>
       </c>
       <c r="T47">
-        <v>1.329031581656009</v>
+        <v>1.35083089682806</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>24.2237677522997</v>
+        <v>23.69716410551058</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0833009543140189</v>
+        <v>0.08316746558599278</v>
       </c>
       <c r="C48">
-        <v>12310.96452763215</v>
+        <v>12184.66722060137</v>
       </c>
       <c r="D48">
-        <v>18310.67852763215</v>
+        <v>18376.09022060137</v>
       </c>
       <c r="E48">
-        <v>2906.014000000001</v>
+        <v>3097.723000000002</v>
       </c>
       <c r="F48">
-        <v>8818.614000000001</v>
+        <v>9010.323000000002</v>
       </c>
       <c r="G48">
         <v>2818.9</v>
@@ -5357,28 +5357,28 @@
         <v>10511.5</v>
       </c>
       <c r="M48">
-        <v>443.5762842</v>
+        <v>453.2192469000001</v>
       </c>
       <c r="N48">
-        <v>10067.9237158</v>
+        <v>10058.2807531</v>
       </c>
       <c r="O48">
-        <v>1912.905506002</v>
+        <v>1911.073343089</v>
       </c>
       <c r="P48">
-        <v>8155.018209798</v>
+        <v>8147.207410011</v>
       </c>
       <c r="Q48">
-        <v>8539.518209798</v>
+        <v>8531.707410011</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1195540265074424</v>
+        <v>0.1207891614830052</v>
       </c>
       <c r="T48">
-        <v>1.35083089682806</v>
+        <v>1.37345282766698</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>23.69716410551058</v>
+        <v>23.19296912454227</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08316746558599278</v>
+        <v>0.08303397685796667</v>
       </c>
       <c r="C49">
-        <v>12184.66722060137</v>
+        <v>12058.83893269931</v>
       </c>
       <c r="D49">
-        <v>18376.09022060137</v>
+        <v>18441.97093269931</v>
       </c>
       <c r="E49">
-        <v>3097.723000000002</v>
+        <v>3289.432000000001</v>
       </c>
       <c r="F49">
-        <v>9010.323000000002</v>
+        <v>9202.032000000001</v>
       </c>
       <c r="G49">
         <v>2818.9</v>
@@ -5439,28 +5439,28 @@
         <v>10511.5</v>
       </c>
       <c r="M49">
-        <v>453.2192469000001</v>
+        <v>462.8622096</v>
       </c>
       <c r="N49">
-        <v>10058.2807531</v>
+        <v>10048.6377904</v>
       </c>
       <c r="O49">
-        <v>1911.073343089</v>
+        <v>1909.241180176</v>
       </c>
       <c r="P49">
-        <v>8147.207410011</v>
+        <v>8139.396610224</v>
       </c>
       <c r="Q49">
-        <v>8531.707410011</v>
+        <v>8523.896610224001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1207891614830052</v>
+        <v>0.1220718016499359</v>
       </c>
       <c r="T49">
-        <v>1.37345282766698</v>
+        <v>1.396944832768936</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>23.19296912454227</v>
+        <v>22.70978226778097</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08303397685796665</v>
+        <v>0.08290048812994054</v>
       </c>
       <c r="C50">
-        <v>12058.83893269932</v>
+        <v>11933.48472656291</v>
       </c>
       <c r="D50">
-        <v>18441.97093269932</v>
+        <v>18508.32572656291</v>
       </c>
       <c r="E50">
-        <v>3289.432000000001</v>
+        <v>3481.141</v>
       </c>
       <c r="F50">
-        <v>9202.032000000001</v>
+        <v>9393.741</v>
       </c>
       <c r="G50">
         <v>2818.9</v>
@@ -5521,28 +5521,28 @@
         <v>10511.5</v>
       </c>
       <c r="M50">
-        <v>462.8622096</v>
+        <v>472.5051723</v>
       </c>
       <c r="N50">
-        <v>10048.6377904</v>
+        <v>10038.9948277</v>
       </c>
       <c r="O50">
-        <v>1909.241180176</v>
+        <v>1907.409017263</v>
       </c>
       <c r="P50">
-        <v>8139.396610224</v>
+        <v>8131.585810437</v>
       </c>
       <c r="Q50">
-        <v>8523.896610224001</v>
+        <v>8516.085810437</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1220718016499359</v>
+        <v>0.123404741431256</v>
       </c>
       <c r="T50">
-        <v>1.396944832768936</v>
+        <v>1.421358092972929</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>22.70978226778097</v>
+        <v>22.24631732354055</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08290048812994054</v>
+        <v>0.08276699940191441</v>
       </c>
       <c r="C51">
-        <v>11933.48472656291</v>
+        <v>11808.60973795427</v>
       </c>
       <c r="D51">
-        <v>18508.32572656291</v>
+        <v>18575.15973795427</v>
       </c>
       <c r="E51">
-        <v>3481.141</v>
+        <v>3672.85</v>
       </c>
       <c r="F51">
-        <v>9393.741</v>
+        <v>9585.450000000001</v>
       </c>
       <c r="G51">
         <v>2818.9</v>
@@ -5603,28 +5603,28 @@
         <v>10511.5</v>
       </c>
       <c r="M51">
-        <v>472.5051723</v>
+        <v>482.148135</v>
       </c>
       <c r="N51">
-        <v>10038.9948277</v>
+        <v>10029.351865</v>
       </c>
       <c r="O51">
-        <v>1907.409017263</v>
+        <v>1905.57685435</v>
       </c>
       <c r="P51">
-        <v>8131.585810437</v>
+        <v>8123.775010650001</v>
       </c>
       <c r="Q51">
-        <v>8516.085810437</v>
+        <v>8508.275010650001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.123404741431256</v>
+        <v>0.1247909988038288</v>
       </c>
       <c r="T51">
-        <v>1.421358092972929</v>
+        <v>1.446747883585082</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>22.24631732354055</v>
+        <v>21.80139097706973</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08276699940191441</v>
+        <v>0.0826335106738883</v>
       </c>
       <c r="C52">
-        <v>11808.60973795427</v>
+        <v>11684.21917708582</v>
       </c>
       <c r="D52">
-        <v>18575.15973795427</v>
+        <v>18642.47817708582</v>
       </c>
       <c r="E52">
-        <v>3672.85</v>
+        <v>3864.559000000001</v>
       </c>
       <c r="F52">
-        <v>9585.450000000001</v>
+        <v>9777.159000000001</v>
       </c>
       <c r="G52">
         <v>2818.9</v>
@@ -5685,28 +5685,28 @@
         <v>10511.5</v>
       </c>
       <c r="M52">
-        <v>482.148135</v>
+        <v>491.7910977</v>
       </c>
       <c r="N52">
-        <v>10029.351865</v>
+        <v>10019.7089023</v>
       </c>
       <c r="O52">
-        <v>1905.57685435</v>
+        <v>1903.744691437</v>
       </c>
       <c r="P52">
-        <v>8123.775010650001</v>
+        <v>8115.964210863001</v>
       </c>
       <c r="Q52">
-        <v>8508.275010650001</v>
+        <v>8500.464210863</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1247909988038288</v>
+        <v>0.1262338381099761</v>
       </c>
       <c r="T52">
-        <v>1.446747883585082</v>
+        <v>1.473173992181404</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>21.80139097706973</v>
+        <v>21.37391272261739</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0826335106738883</v>
+        <v>0.08250002194586219</v>
       </c>
       <c r="C53">
-        <v>11684.21917708582</v>
+        <v>11560.31832997425</v>
       </c>
       <c r="D53">
-        <v>18642.47817708582</v>
+        <v>18710.28632997425</v>
       </c>
       <c r="E53">
-        <v>3864.559000000001</v>
+        <v>4056.268</v>
       </c>
       <c r="F53">
-        <v>9777.159000000001</v>
+        <v>9968.868</v>
       </c>
       <c r="G53">
         <v>2818.9</v>
@@ -5767,28 +5767,28 @@
         <v>10511.5</v>
       </c>
       <c r="M53">
-        <v>491.7910977</v>
+        <v>501.4340604</v>
       </c>
       <c r="N53">
-        <v>10019.7089023</v>
+        <v>10010.0659396</v>
       </c>
       <c r="O53">
-        <v>1903.744691437</v>
+        <v>1901.912528524</v>
       </c>
       <c r="P53">
-        <v>8115.964210863001</v>
+        <v>8108.153411075999</v>
       </c>
       <c r="Q53">
-        <v>8500.464210863</v>
+        <v>8492.653411076</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1262338381099761</v>
+        <v>0.1277367957205462</v>
       </c>
       <c r="T53">
-        <v>1.473173992181404</v>
+        <v>1.500701188635907</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>21.37391272261739</v>
+        <v>20.96287593949013</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08250002194586219</v>
+        <v>0.08236653321783606</v>
       </c>
       <c r="C54">
-        <v>11560.31832997425</v>
+        <v>11436.91255982418</v>
       </c>
       <c r="D54">
-        <v>18710.28632997425</v>
+        <v>18778.58955982418</v>
       </c>
       <c r="E54">
-        <v>4056.268</v>
+        <v>4247.977000000001</v>
       </c>
       <c r="F54">
-        <v>9968.868</v>
+        <v>10160.577</v>
       </c>
       <c r="G54">
         <v>2818.9</v>
@@ -5849,28 +5849,28 @@
         <v>10511.5</v>
       </c>
       <c r="M54">
-        <v>501.4340604</v>
+        <v>511.0770231</v>
       </c>
       <c r="N54">
-        <v>10010.0659396</v>
+        <v>10000.4229769</v>
       </c>
       <c r="O54">
-        <v>1901.912528524</v>
+        <v>1900.080365611</v>
       </c>
       <c r="P54">
-        <v>8108.153411075999</v>
+        <v>8100.342611288999</v>
       </c>
       <c r="Q54">
-        <v>8492.653411076</v>
+        <v>8484.842611288999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1277367957205462</v>
+        <v>0.1293037089741193</v>
       </c>
       <c r="T54">
-        <v>1.500701188635907</v>
+        <v>1.529399755152303</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>20.96287593949013</v>
+        <v>20.56734997836767</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08236653321783606</v>
+        <v>0.08223304448980995</v>
       </c>
       <c r="C55">
-        <v>11436.91255982418</v>
+        <v>11314.00730844218</v>
       </c>
       <c r="D55">
-        <v>18778.58955982418</v>
+        <v>18847.39330844218</v>
       </c>
       <c r="E55">
-        <v>4247.977000000001</v>
+        <v>4439.686000000002</v>
       </c>
       <c r="F55">
-        <v>10160.577</v>
+        <v>10352.286</v>
       </c>
       <c r="G55">
         <v>2818.9</v>
@@ -5931,28 +5931,28 @@
         <v>10511.5</v>
       </c>
       <c r="M55">
-        <v>511.0770231</v>
+        <v>520.7199858</v>
       </c>
       <c r="N55">
-        <v>10000.4229769</v>
+        <v>9990.7800142</v>
       </c>
       <c r="O55">
-        <v>1900.080365611</v>
+        <v>1898.248202698</v>
       </c>
       <c r="P55">
-        <v>8100.342611288999</v>
+        <v>8092.531811502</v>
       </c>
       <c r="Q55">
-        <v>8484.842611288999</v>
+        <v>8477.031811502</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1293037089741193</v>
+        <v>0.1309387488908912</v>
       </c>
       <c r="T55">
-        <v>1.529399755152303</v>
+        <v>1.559346085430282</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>20.56734997836767</v>
+        <v>20.18647312691642</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08223304448980995</v>
+        <v>0.08209955576178382</v>
       </c>
       <c r="C56">
-        <v>11314.00730844218</v>
+        <v>11191.6080976821</v>
       </c>
       <c r="D56">
-        <v>18847.39330844218</v>
+        <v>18916.7030976821</v>
       </c>
       <c r="E56">
-        <v>4439.686000000002</v>
+        <v>4631.395</v>
       </c>
       <c r="F56">
-        <v>10352.286</v>
+        <v>10543.995</v>
       </c>
       <c r="G56">
         <v>2818.9</v>
@@ -6013,28 +6013,28 @@
         <v>10511.5</v>
       </c>
       <c r="M56">
-        <v>520.7199858</v>
+        <v>530.3629485</v>
       </c>
       <c r="N56">
-        <v>9990.7800142</v>
+        <v>9981.1370515</v>
       </c>
       <c r="O56">
-        <v>1898.248202698</v>
+        <v>1896.416039785</v>
       </c>
       <c r="P56">
-        <v>8092.531811502</v>
+        <v>8084.721011715</v>
       </c>
       <c r="Q56">
-        <v>8477.031811502</v>
+        <v>8469.221011714999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1309387488908912</v>
+        <v>0.1326464572484085</v>
       </c>
       <c r="T56">
-        <v>1.559346085430282</v>
+        <v>1.590623363720615</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>20.18647312691642</v>
+        <v>19.81944634279067</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08209955576178382</v>
+        <v>0.08196606703375769</v>
       </c>
       <c r="C57">
-        <v>11191.6080976821</v>
+        <v>11069.72053092228</v>
       </c>
       <c r="D57">
-        <v>18916.7030976821</v>
+        <v>18986.52453092228</v>
       </c>
       <c r="E57">
-        <v>4631.395</v>
+        <v>4823.104000000001</v>
       </c>
       <c r="F57">
-        <v>10543.995</v>
+        <v>10735.704</v>
       </c>
       <c r="G57">
         <v>2818.9</v>
@@ -6095,28 +6095,28 @@
         <v>10511.5</v>
       </c>
       <c r="M57">
-        <v>530.3629485</v>
+        <v>540.0059112</v>
       </c>
       <c r="N57">
-        <v>9981.1370515</v>
+        <v>9971.4940888</v>
       </c>
       <c r="O57">
-        <v>1896.416039785</v>
+        <v>1894.583876872</v>
       </c>
       <c r="P57">
-        <v>8084.721011715</v>
+        <v>8076.910211928</v>
       </c>
       <c r="Q57">
-        <v>8469.221011714999</v>
+        <v>8461.410211928</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1326464572484085</v>
+        <v>0.1344317887130857</v>
       </c>
       <c r="T57">
-        <v>1.590623363720615</v>
+        <v>1.623322336478691</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>19.81944634279067</v>
+        <v>19.46552765809798</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08196606703375769</v>
+        <v>0.0818325783057316</v>
       </c>
       <c r="C58">
-        <v>11069.72053092228</v>
+        <v>10948.35029457568</v>
       </c>
       <c r="D58">
-        <v>18986.52453092228</v>
+        <v>19056.86329457568</v>
       </c>
       <c r="E58">
-        <v>4823.104000000001</v>
+        <v>5014.813000000002</v>
       </c>
       <c r="F58">
-        <v>10735.704</v>
+        <v>10927.413</v>
       </c>
       <c r="G58">
         <v>2818.9</v>
@@ -6177,28 +6177,28 @@
         <v>10511.5</v>
       </c>
       <c r="M58">
-        <v>540.0059112</v>
+        <v>549.6488739000001</v>
       </c>
       <c r="N58">
-        <v>9971.4940888</v>
+        <v>9961.8511261</v>
       </c>
       <c r="O58">
-        <v>1894.583876872</v>
+        <v>1892.751713959</v>
       </c>
       <c r="P58">
-        <v>8076.910211928</v>
+        <v>8069.099412141</v>
       </c>
       <c r="Q58">
-        <v>8461.410211928</v>
+        <v>8453.599412141</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1344317887130857</v>
+        <v>0.1363001588505386</v>
       </c>
       <c r="T58">
-        <v>1.623322336478691</v>
+        <v>1.65754219169063</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>19.46552765809798</v>
+        <v>19.12402717286819</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0818325783057316</v>
+        <v>0.08169908957770547</v>
       </c>
       <c r="C59">
-        <v>10948.35029457568</v>
+        <v>10827.50315963368</v>
       </c>
       <c r="D59">
-        <v>19056.86329457568</v>
+        <v>19127.72515963368</v>
       </c>
       <c r="E59">
-        <v>5014.813000000002</v>
+        <v>5206.522000000003</v>
       </c>
       <c r="F59">
-        <v>10927.413</v>
+        <v>11119.122</v>
       </c>
       <c r="G59">
         <v>2818.9</v>
@@ -6259,28 +6259,28 @@
         <v>10511.5</v>
       </c>
       <c r="M59">
-        <v>549.6488739000001</v>
+        <v>559.2918366000001</v>
       </c>
       <c r="N59">
-        <v>9961.8511261</v>
+        <v>9952.208163400001</v>
       </c>
       <c r="O59">
-        <v>1892.751713959</v>
+        <v>1890.919551046</v>
       </c>
       <c r="P59">
-        <v>8069.099412141</v>
+        <v>8061.288612354</v>
       </c>
       <c r="Q59">
-        <v>8453.599412141</v>
+        <v>8445.788612354001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1363001588505386</v>
+        <v>0.1382574989945368</v>
       </c>
       <c r="T59">
-        <v>1.65754219169063</v>
+        <v>1.693391563817425</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>19.12402717286819</v>
+        <v>18.79430256643942</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08169908957770547</v>
+        <v>0.08156560084967936</v>
       </c>
       <c r="C60">
-        <v>10827.50315963368</v>
+        <v>10707.18498324445</v>
       </c>
       <c r="D60">
-        <v>19127.72515963368</v>
+        <v>19199.11598324445</v>
       </c>
       <c r="E60">
-        <v>5206.521999999999</v>
+        <v>5398.231</v>
       </c>
       <c r="F60">
-        <v>11119.122</v>
+        <v>11310.831</v>
       </c>
       <c r="G60">
         <v>2818.9</v>
@@ -6341,28 +6341,28 @@
         <v>10511.5</v>
       </c>
       <c r="M60">
-        <v>559.2918365999999</v>
+        <v>568.9347993</v>
       </c>
       <c r="N60">
-        <v>9952.208163400001</v>
+        <v>9942.565200700001</v>
       </c>
       <c r="O60">
-        <v>1890.919551046</v>
+        <v>1889.087388133</v>
       </c>
       <c r="P60">
-        <v>8061.288612354</v>
+        <v>8053.477812567001</v>
       </c>
       <c r="Q60">
-        <v>8445.788612354001</v>
+        <v>8437.977812567002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1382574989945368</v>
+        <v>0.1403103191455594</v>
       </c>
       <c r="T60">
-        <v>1.693391563817424</v>
+        <v>1.730989685804062</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>18.79430256643943</v>
+        <v>18.47575506531334</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08156560084967936</v>
+        <v>0.08143211212165323</v>
       </c>
       <c r="C61">
-        <v>10707.18498324445</v>
+        <v>10587.40171032679</v>
       </c>
       <c r="D61">
-        <v>19199.11598324445</v>
+        <v>19271.04171032679</v>
       </c>
       <c r="E61">
-        <v>5398.231</v>
+        <v>5589.940000000001</v>
       </c>
       <c r="F61">
-        <v>11310.831</v>
+        <v>11502.54</v>
       </c>
       <c r="G61">
         <v>2818.9</v>
@@ -6423,28 +6423,28 @@
         <v>10511.5</v>
       </c>
       <c r="M61">
-        <v>568.9347993</v>
+        <v>578.577762</v>
       </c>
       <c r="N61">
-        <v>9942.565200700001</v>
+        <v>9932.922237999999</v>
       </c>
       <c r="O61">
-        <v>1889.087388133</v>
+        <v>1887.25522522</v>
       </c>
       <c r="P61">
-        <v>8053.477812567001</v>
+        <v>8045.667012779999</v>
       </c>
       <c r="Q61">
-        <v>8437.977812567002</v>
+        <v>8430.167012779999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1403103191455594</v>
+        <v>0.1424657803041331</v>
       </c>
       <c r="T61">
-        <v>1.730989685804062</v>
+        <v>1.770467713890031</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>18.47575506531334</v>
+        <v>18.16782581422478</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08143211212165323</v>
+        <v>0.08129862339362712</v>
       </c>
       <c r="C62">
-        <v>10587.40171032679</v>
+        <v>10468.15937522038</v>
       </c>
       <c r="D62">
-        <v>19271.04171032679</v>
+        <v>19343.50837522038</v>
       </c>
       <c r="E62">
-        <v>5589.940000000001</v>
+        <v>5781.648999999999</v>
       </c>
       <c r="F62">
-        <v>11502.54</v>
+        <v>11694.249</v>
       </c>
       <c r="G62">
         <v>2818.9</v>
@@ -6505,28 +6505,28 @@
         <v>10511.5</v>
       </c>
       <c r="M62">
-        <v>578.577762</v>
+        <v>588.2207247</v>
       </c>
       <c r="N62">
-        <v>9932.922237999999</v>
+        <v>9923.279275299999</v>
       </c>
       <c r="O62">
-        <v>1887.25522522</v>
+        <v>1885.423062307</v>
       </c>
       <c r="P62">
-        <v>8045.667012779999</v>
+        <v>8037.856212993</v>
       </c>
       <c r="Q62">
-        <v>8430.167012779999</v>
+        <v>8422.356212993</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1424657803041331</v>
+        <v>0.1447317779323772</v>
       </c>
       <c r="T62">
-        <v>1.770467713890031</v>
+        <v>1.81197025623682</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>18.16782581422478</v>
+        <v>17.86999260415552</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08129862339362712</v>
+        <v>0.08116513466560099</v>
       </c>
       <c r="C63">
-        <v>10468.15937522038</v>
+        <v>10349.46410337345</v>
       </c>
       <c r="D63">
-        <v>19343.50837522038</v>
+        <v>19416.52210337345</v>
       </c>
       <c r="E63">
-        <v>5781.648999999999</v>
+        <v>5973.358</v>
       </c>
       <c r="F63">
-        <v>11694.249</v>
+        <v>11885.958</v>
       </c>
       <c r="G63">
         <v>2818.9</v>
@@ -6587,28 +6587,28 @@
         <v>10511.5</v>
       </c>
       <c r="M63">
-        <v>588.2207247</v>
+        <v>597.8636874</v>
       </c>
       <c r="N63">
-        <v>9923.279275299999</v>
+        <v>9913.6363126</v>
       </c>
       <c r="O63">
-        <v>1885.423062307</v>
+        <v>1883.590899394</v>
       </c>
       <c r="P63">
-        <v>8037.856212993</v>
+        <v>8030.045413205999</v>
       </c>
       <c r="Q63">
-        <v>8422.356212993</v>
+        <v>8414.545413206</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1447317779323772</v>
+        <v>0.1471170385936868</v>
       </c>
       <c r="T63">
-        <v>1.81197025623682</v>
+        <v>1.855657142917649</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>17.86999260415552</v>
+        <v>17.58176691699172</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08116513466560099</v>
+        <v>0.08103164593757486</v>
       </c>
       <c r="C64">
-        <v>10349.46410337345</v>
+        <v>10231.32211306874</v>
       </c>
       <c r="D64">
-        <v>19416.52210337345</v>
+        <v>19490.08911306874</v>
       </c>
       <c r="E64">
-        <v>5973.358</v>
+        <v>6165.067000000001</v>
       </c>
       <c r="F64">
-        <v>11885.958</v>
+        <v>12077.667</v>
       </c>
       <c r="G64">
         <v>2818.9</v>
@@ -6669,28 +6669,28 @@
         <v>10511.5</v>
       </c>
       <c r="M64">
-        <v>597.8636874</v>
+        <v>607.5066501</v>
       </c>
       <c r="N64">
-        <v>9913.6363126</v>
+        <v>9903.9933499</v>
       </c>
       <c r="O64">
-        <v>1883.590899394</v>
+        <v>1881.758736481</v>
       </c>
       <c r="P64">
-        <v>8030.045413205999</v>
+        <v>8022.234613419</v>
       </c>
       <c r="Q64">
-        <v>8414.545413206</v>
+        <v>8406.734613419001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1471170385936868</v>
+        <v>0.1496312322637159</v>
       </c>
       <c r="T64">
-        <v>1.855657142917649</v>
+        <v>1.901705482932578</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>17.58176691699172</v>
+        <v>17.30269125164265</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08103164593757486</v>
+        <v>0.08089815720954877</v>
       </c>
       <c r="C65">
-        <v>10231.32211306874</v>
+        <v>10113.73971718888</v>
       </c>
       <c r="D65">
-        <v>19490.08911306874</v>
+        <v>19564.21571718888</v>
       </c>
       <c r="E65">
-        <v>6165.067000000001</v>
+        <v>6356.776000000002</v>
       </c>
       <c r="F65">
-        <v>12077.667</v>
+        <v>12269.376</v>
       </c>
       <c r="G65">
         <v>2818.9</v>
@@ -6751,28 +6751,28 @@
         <v>10511.5</v>
       </c>
       <c r="M65">
-        <v>607.5066501</v>
+        <v>617.1496128000001</v>
       </c>
       <c r="N65">
-        <v>9903.9933499</v>
+        <v>9894.3503872</v>
       </c>
       <c r="O65">
-        <v>1881.758736481</v>
+        <v>1879.926573568</v>
       </c>
       <c r="P65">
-        <v>8022.234613419</v>
+        <v>8014.423813632</v>
       </c>
       <c r="Q65">
-        <v>8406.734613419001</v>
+        <v>8398.923813632</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1496312322637159</v>
+        <v>0.1522851033598577</v>
       </c>
       <c r="T65">
-        <v>1.901705482932578</v>
+        <v>1.950312064059448</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>17.30269125164265</v>
+        <v>17.03233670083573</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08089815720954877</v>
+        <v>0.08076466848152264</v>
       </c>
       <c r="C66">
-        <v>10113.73971718888</v>
+        <v>9996.723325022313</v>
       </c>
       <c r="D66">
-        <v>19564.21571718888</v>
+        <v>19638.90832502231</v>
       </c>
       <c r="E66">
-        <v>6356.776000000002</v>
+        <v>6548.485000000001</v>
       </c>
       <c r="F66">
-        <v>12269.376</v>
+        <v>12461.085</v>
       </c>
       <c r="G66">
         <v>2818.9</v>
@@ -6833,28 +6833,28 @@
         <v>10511.5</v>
       </c>
       <c r="M66">
-        <v>617.1496128000001</v>
+        <v>626.7925755</v>
       </c>
       <c r="N66">
-        <v>9894.3503872</v>
+        <v>9884.7074245</v>
       </c>
       <c r="O66">
-        <v>1879.926573568</v>
+        <v>1878.094410655</v>
       </c>
       <c r="P66">
-        <v>8014.423813632</v>
+        <v>8006.613013845001</v>
       </c>
       <c r="Q66">
-        <v>8398.923813632</v>
+        <v>8391.113013845001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1522851033598577</v>
+        <v>0.1550906242329218</v>
       </c>
       <c r="T66">
-        <v>1.950312064059448</v>
+        <v>2.001696164107852</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>17.03233670083573</v>
+        <v>16.7703007515921</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08076466848152264</v>
+        <v>0.08063117975349651</v>
       </c>
       <c r="C67">
-        <v>9996.723325022313</v>
+        <v>9880.2794441105</v>
       </c>
       <c r="D67">
-        <v>19638.90832502231</v>
+        <v>19714.1734441105</v>
       </c>
       <c r="E67">
-        <v>6548.485000000001</v>
+        <v>6740.194000000001</v>
       </c>
       <c r="F67">
-        <v>12461.085</v>
+        <v>12652.794</v>
       </c>
       <c r="G67">
         <v>2818.9</v>
@@ -6915,28 +6915,28 @@
         <v>10511.5</v>
       </c>
       <c r="M67">
-        <v>626.7925755</v>
+        <v>636.4355382</v>
       </c>
       <c r="N67">
-        <v>9884.7074245</v>
+        <v>9875.064461800001</v>
       </c>
       <c r="O67">
-        <v>1878.094410655</v>
+        <v>1876.262247742</v>
       </c>
       <c r="P67">
-        <v>8006.613013845001</v>
+        <v>7998.802214058001</v>
       </c>
       <c r="Q67">
-        <v>8391.113013845001</v>
+        <v>8383.302214058</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1550906242329218</v>
+        <v>0.158061175745578</v>
       </c>
       <c r="T67">
-        <v>2.001696164107852</v>
+        <v>2.056102858276751</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>16.7703007515921</v>
+        <v>16.51620528565889</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08063117975349651</v>
+        <v>0.0804976910254704</v>
       </c>
       <c r="C68">
-        <v>9880.2794441105</v>
+        <v>9764.414682138</v>
       </c>
       <c r="D68">
-        <v>19714.1734441105</v>
+        <v>19790.017682138</v>
       </c>
       <c r="E68">
-        <v>6740.194000000001</v>
+        <v>6931.903000000002</v>
       </c>
       <c r="F68">
-        <v>12652.794</v>
+        <v>12844.503</v>
       </c>
       <c r="G68">
         <v>2818.9</v>
@@ -6997,28 +6997,28 @@
         <v>10511.5</v>
       </c>
       <c r="M68">
-        <v>636.4355382</v>
+        <v>646.0785009000001</v>
       </c>
       <c r="N68">
-        <v>9875.064461800001</v>
+        <v>9865.421499100001</v>
       </c>
       <c r="O68">
-        <v>1876.262247742</v>
+        <v>1874.430084829</v>
       </c>
       <c r="P68">
-        <v>7998.802214058001</v>
+        <v>7990.991414271</v>
       </c>
       <c r="Q68">
-        <v>8383.302214058</v>
+        <v>8375.491414271</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.158061175745578</v>
+        <v>0.1612117606832437</v>
       </c>
       <c r="T68">
-        <v>2.056102858276751</v>
+        <v>2.113806927849826</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>16.51620528565889</v>
+        <v>16.26969475900727</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0804976910254704</v>
+        <v>0.08036420229744427</v>
       </c>
       <c r="C69">
-        <v>9764.414682138</v>
+        <v>9649.135748866271</v>
       </c>
       <c r="D69">
-        <v>19790.017682138</v>
+        <v>19866.44774886627</v>
       </c>
       <c r="E69">
-        <v>6931.903000000002</v>
+        <v>7123.612000000001</v>
       </c>
       <c r="F69">
-        <v>12844.503</v>
+        <v>13036.212</v>
       </c>
       <c r="G69">
         <v>2818.9</v>
@@ -7079,28 +7079,28 @@
         <v>10511.5</v>
       </c>
       <c r="M69">
-        <v>646.0785009000001</v>
+        <v>655.7214636</v>
       </c>
       <c r="N69">
-        <v>9865.421499100001</v>
+        <v>9855.778536399999</v>
       </c>
       <c r="O69">
-        <v>1874.430084829</v>
+        <v>1872.597921916</v>
       </c>
       <c r="P69">
-        <v>7990.991414271</v>
+        <v>7983.180614483999</v>
       </c>
       <c r="Q69">
-        <v>8375.491414271</v>
+        <v>8367.680614483999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1612117606832437</v>
+        <v>0.1645592571795134</v>
       </c>
       <c r="T69">
-        <v>2.113806927849826</v>
+        <v>2.175117501771218</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>16.26969475900727</v>
+        <v>16.03043454196304</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08036420229744427</v>
+        <v>0.08023071356941816</v>
       </c>
       <c r="C70">
-        <v>9649.135748866271</v>
+        <v>9534.44945811238</v>
       </c>
       <c r="D70">
-        <v>19866.44774886627</v>
+        <v>19943.47045811238</v>
       </c>
       <c r="E70">
-        <v>7123.612000000001</v>
+        <v>7315.321000000002</v>
       </c>
       <c r="F70">
-        <v>13036.212</v>
+        <v>13227.921</v>
       </c>
       <c r="G70">
         <v>2818.9</v>
@@ -7161,28 +7161,28 @@
         <v>10511.5</v>
       </c>
       <c r="M70">
-        <v>655.7214636</v>
+        <v>665.3644263000001</v>
       </c>
       <c r="N70">
-        <v>9855.778536399999</v>
+        <v>9846.135573699999</v>
       </c>
       <c r="O70">
-        <v>1872.597921916</v>
+        <v>1870.765759003</v>
       </c>
       <c r="P70">
-        <v>7983.180614483999</v>
+        <v>7975.369814697</v>
       </c>
       <c r="Q70">
-        <v>8367.680614483999</v>
+        <v>8359.869814697</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1645592571795134</v>
+        <v>0.1681227211916715</v>
       </c>
       <c r="T70">
-        <v>2.175117501771218</v>
+        <v>2.240383596590764</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>16.03043454196304</v>
+        <v>15.79810940367372</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08023071356941816</v>
+        <v>0.08009722484139205</v>
       </c>
       <c r="C71">
-        <v>9534.44945811238</v>
+        <v>9420.362729774048</v>
       </c>
       <c r="D71">
-        <v>19943.47045811238</v>
+        <v>20021.09272977405</v>
       </c>
       <c r="E71">
-        <v>7315.321000000002</v>
+        <v>7507.030000000002</v>
       </c>
       <c r="F71">
-        <v>13227.921</v>
+        <v>13419.63</v>
       </c>
       <c r="G71">
         <v>2818.9</v>
@@ -7243,28 +7243,28 @@
         <v>10511.5</v>
       </c>
       <c r="M71">
-        <v>665.3644263000001</v>
+        <v>675.0073890000001</v>
       </c>
       <c r="N71">
-        <v>9846.135573699999</v>
+        <v>9836.492611</v>
       </c>
       <c r="O71">
-        <v>1870.765759003</v>
+        <v>1868.93359609</v>
       </c>
       <c r="P71">
-        <v>7975.369814697</v>
+        <v>7967.55901491</v>
       </c>
       <c r="Q71">
-        <v>8359.869814697</v>
+        <v>8352.059014909999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1681227211916715</v>
+        <v>0.1719237494713068</v>
       </c>
       <c r="T71">
-        <v>2.240383596590764</v>
+        <v>2.31000076439828</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>15.79810940367372</v>
+        <v>15.57242212647838</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08009722484139205</v>
+        <v>0.07996373611336594</v>
       </c>
       <c r="C72">
-        <v>9420.362729774048</v>
+        <v>9306.882591902066</v>
       </c>
       <c r="D72">
-        <v>20021.09272977405</v>
+        <v>20099.32159190207</v>
       </c>
       <c r="E72">
-        <v>7507.030000000002</v>
+        <v>7698.739000000001</v>
       </c>
       <c r="F72">
-        <v>13419.63</v>
+        <v>13611.339</v>
       </c>
       <c r="G72">
         <v>2818.9</v>
@@ -7325,28 +7325,28 @@
         <v>10511.5</v>
       </c>
       <c r="M72">
-        <v>675.0073890000001</v>
+        <v>684.6503517000001</v>
       </c>
       <c r="N72">
-        <v>9836.492611</v>
+        <v>9826.8496483</v>
       </c>
       <c r="O72">
-        <v>1868.93359609</v>
+        <v>1867.101433177</v>
       </c>
       <c r="P72">
-        <v>7967.55901491</v>
+        <v>7959.748215123</v>
       </c>
       <c r="Q72">
-        <v>8352.059014909999</v>
+        <v>8344.248215123</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1719237494713068</v>
+        <v>0.1759869176322963</v>
       </c>
       <c r="T72">
-        <v>2.31000076439828</v>
+        <v>2.384419116192522</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>15.57242212647838</v>
+        <v>15.35309223737305</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07996373611336594</v>
+        <v>0.07983024738533981</v>
       </c>
       <c r="C73">
-        <v>9306.882591902067</v>
+        <v>9194.016182821544</v>
       </c>
       <c r="D73">
-        <v>20099.32159190207</v>
+        <v>20178.16418282154</v>
       </c>
       <c r="E73">
-        <v>7698.739</v>
+        <v>7890.448</v>
       </c>
       <c r="F73">
-        <v>13611.339</v>
+        <v>13803.048</v>
       </c>
       <c r="G73">
         <v>2818.9</v>
@@ -7407,28 +7407,28 @@
         <v>10511.5</v>
       </c>
       <c r="M73">
-        <v>684.6503517</v>
+        <v>694.2933144</v>
       </c>
       <c r="N73">
-        <v>9826.8496483</v>
+        <v>9817.2066856</v>
       </c>
       <c r="O73">
-        <v>1867.101433177</v>
+        <v>1865.269270264</v>
       </c>
       <c r="P73">
-        <v>7959.748215123</v>
+        <v>7951.937415336</v>
       </c>
       <c r="Q73">
-        <v>8344.248215123</v>
+        <v>8336.437415336</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1759869176322963</v>
+        <v>0.1803403120904993</v>
       </c>
       <c r="T73">
-        <v>2.384419116192521</v>
+        <v>2.464153064543494</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>15.35309223737305</v>
+        <v>15.13985484518732</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07983024738533981</v>
+        <v>0.0796967586573137</v>
       </c>
       <c r="C74">
-        <v>9194.016182821544</v>
+        <v>9081.770753303252</v>
       </c>
       <c r="D74">
-        <v>20178.16418282154</v>
+        <v>20257.62775330325</v>
       </c>
       <c r="E74">
-        <v>7890.448</v>
+        <v>8082.157000000001</v>
       </c>
       <c r="F74">
-        <v>13803.048</v>
+        <v>13994.757</v>
       </c>
       <c r="G74">
         <v>2818.9</v>
@@ -7489,28 +7489,28 @@
         <v>10511.5</v>
       </c>
       <c r="M74">
-        <v>694.2933144</v>
+        <v>703.9362771</v>
       </c>
       <c r="N74">
-        <v>9817.2066856</v>
+        <v>9807.5637229</v>
       </c>
       <c r="O74">
-        <v>1865.269270264</v>
+        <v>1863.437107351</v>
       </c>
       <c r="P74">
-        <v>7951.937415336</v>
+        <v>7944.126615549</v>
       </c>
       <c r="Q74">
-        <v>8336.437415336</v>
+        <v>8328.626615549001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1803403120904993</v>
+        <v>0.1850161802122729</v>
       </c>
       <c r="T74">
-        <v>2.464153064543494</v>
+        <v>2.549793231290835</v>
       </c>
       <c r="U74">
         <v>0.0503</v>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>15.13985484518732</v>
+        <v>14.93245957333544</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0796967586573137</v>
+        <v>0.07956326992928757</v>
       </c>
       <c r="C75">
-        <v>9081.770753303252</v>
+        <v>8970.153668786519</v>
       </c>
       <c r="D75">
-        <v>20257.62775330325</v>
+        <v>20337.71966878652</v>
       </c>
       <c r="E75">
-        <v>8082.157000000001</v>
+        <v>8273.866</v>
       </c>
       <c r="F75">
-        <v>13994.757</v>
+        <v>14186.466</v>
       </c>
       <c r="G75">
         <v>2818.9</v>
@@ -7571,28 +7571,28 @@
         <v>10511.5</v>
       </c>
       <c r="M75">
-        <v>703.9362771</v>
+        <v>713.5792398</v>
       </c>
       <c r="N75">
-        <v>9807.5637229</v>
+        <v>9797.920760200001</v>
       </c>
       <c r="O75">
-        <v>1863.437107351</v>
+        <v>1861.604944438</v>
       </c>
       <c r="P75">
-        <v>7944.126615549</v>
+        <v>7936.315815762</v>
       </c>
       <c r="Q75">
-        <v>8328.626615549001</v>
+        <v>8320.815815762</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1850161802122729</v>
+        <v>0.1900517304972599</v>
       </c>
       <c r="T75">
-        <v>2.549793231290835</v>
+        <v>2.642021103172587</v>
       </c>
       <c r="U75">
         <v>0.0503</v>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>14.93245957333544</v>
+        <v>14.73066957910117</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07956326992928757</v>
+        <v>0.07942978120126146</v>
       </c>
       <c r="C76">
-        <v>8970.153668786519</v>
+        <v>8859.172411654976</v>
       </c>
       <c r="D76">
-        <v>20337.71966878652</v>
+        <v>20418.44741165498</v>
       </c>
       <c r="E76">
-        <v>8273.866</v>
+        <v>8465.575000000001</v>
       </c>
       <c r="F76">
-        <v>14186.466</v>
+        <v>14378.175</v>
       </c>
       <c r="G76">
         <v>2818.9</v>
@@ -7653,28 +7653,28 @@
         <v>10511.5</v>
       </c>
       <c r="M76">
-        <v>713.5792398</v>
+        <v>723.2222025</v>
       </c>
       <c r="N76">
-        <v>9797.920760200001</v>
+        <v>9788.277797500001</v>
       </c>
       <c r="O76">
-        <v>1861.604944438</v>
+        <v>1859.772781525</v>
       </c>
       <c r="P76">
-        <v>7936.315815762</v>
+        <v>7928.505015975001</v>
       </c>
       <c r="Q76">
-        <v>8320.815815762</v>
+        <v>8313.005015975001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1900517304972599</v>
+        <v>0.1954901248050458</v>
       </c>
       <c r="T76">
-        <v>2.642021103172587</v>
+        <v>2.741627204804879</v>
       </c>
       <c r="U76">
         <v>0.0503</v>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>14.73066957910117</v>
+        <v>14.53426065137982</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07942978120126146</v>
+        <v>0.07929629247323534</v>
       </c>
       <c r="C77">
-        <v>8859.172411654976</v>
+        <v>8748.834583566848</v>
       </c>
       <c r="D77">
-        <v>20418.44741165498</v>
+        <v>20499.81858356685</v>
       </c>
       <c r="E77">
-        <v>8465.575000000001</v>
+        <v>8657.284000000001</v>
       </c>
       <c r="F77">
-        <v>14378.175</v>
+        <v>14569.884</v>
       </c>
       <c r="G77">
         <v>2818.9</v>
@@ -7735,28 +7735,28 @@
         <v>10511.5</v>
       </c>
       <c r="M77">
-        <v>723.2222025</v>
+        <v>732.8651652000001</v>
       </c>
       <c r="N77">
-        <v>9788.277797500001</v>
+        <v>9778.634834799999</v>
       </c>
       <c r="O77">
-        <v>1859.772781525</v>
+        <v>1857.940618612</v>
       </c>
       <c r="P77">
-        <v>7928.505015975001</v>
+        <v>7920.694216188</v>
       </c>
       <c r="Q77">
-        <v>8313.005015975001</v>
+        <v>8305.194216188</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1954901248050458</v>
+        <v>0.2013817186384806</v>
       </c>
       <c r="T77">
-        <v>2.741627204804879</v>
+        <v>2.849533814906529</v>
       </c>
       <c r="U77">
         <v>0.0503</v>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>14.53426065137982</v>
+        <v>14.34302037965114</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07929629247323534</v>
+        <v>0.07916280374520922</v>
       </c>
       <c r="C78">
-        <v>8748.834583566848</v>
+        <v>8639.14790784107</v>
       </c>
       <c r="D78">
-        <v>20499.81858356685</v>
+        <v>20581.84090784107</v>
       </c>
       <c r="E78">
-        <v>8657.284000000001</v>
+        <v>8848.993</v>
       </c>
       <c r="F78">
-        <v>14569.884</v>
+        <v>14761.593</v>
       </c>
       <c r="G78">
         <v>2818.9</v>
@@ -7817,28 +7817,28 @@
         <v>10511.5</v>
       </c>
       <c r="M78">
-        <v>732.8651652000001</v>
+        <v>742.5081279</v>
       </c>
       <c r="N78">
-        <v>9778.634834799999</v>
+        <v>9768.991872099999</v>
       </c>
       <c r="O78">
-        <v>1857.940618612</v>
+        <v>1856.108455699</v>
       </c>
       <c r="P78">
-        <v>7920.694216188</v>
+        <v>7912.883416401</v>
       </c>
       <c r="Q78">
-        <v>8305.194216188</v>
+        <v>8297.383416401</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2013817186384806</v>
+        <v>0.2077856249791705</v>
       </c>
       <c r="T78">
-        <v>2.849533814906529</v>
+        <v>2.966823608495279</v>
       </c>
       <c r="U78">
         <v>0.0503</v>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>14.34302037965114</v>
+        <v>14.15674738770762</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07916280374520922</v>
+        <v>0.0790293150171831</v>
       </c>
       <c r="C79">
-        <v>8639.14790784107</v>
+        <v>8530.120231900944</v>
       </c>
       <c r="D79">
-        <v>20581.84090784107</v>
+        <v>20664.52223190094</v>
       </c>
       <c r="E79">
-        <v>8848.993</v>
+        <v>9040.702000000001</v>
       </c>
       <c r="F79">
-        <v>14761.593</v>
+        <v>14953.302</v>
       </c>
       <c r="G79">
         <v>2818.9</v>
@@ -7899,28 +7899,28 @@
         <v>10511.5</v>
       </c>
       <c r="M79">
-        <v>742.5081279</v>
+        <v>752.1510906000001</v>
       </c>
       <c r="N79">
-        <v>9768.991872099999</v>
+        <v>9759.3489094</v>
       </c>
       <c r="O79">
-        <v>1856.108455699</v>
+        <v>1854.276292786</v>
       </c>
       <c r="P79">
-        <v>7912.883416401</v>
+        <v>7905.072616613999</v>
       </c>
       <c r="Q79">
-        <v>8297.383416401</v>
+        <v>8289.572616613999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2077856249791705</v>
+        <v>0.2147717046235595</v>
       </c>
       <c r="T79">
-        <v>2.966823608495279</v>
+        <v>3.094776110592097</v>
       </c>
       <c r="U79">
         <v>0.0503</v>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>14.15674738770762</v>
+        <v>13.97525062632675</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0790293150171831</v>
+        <v>0.07889582628915698</v>
       </c>
       <c r="C80">
-        <v>8530.120231900944</v>
+        <v>8421.759529777039</v>
       </c>
       <c r="D80">
-        <v>20664.52223190094</v>
+        <v>20747.87052977704</v>
       </c>
       <c r="E80">
-        <v>9040.702000000001</v>
+        <v>9232.411000000002</v>
       </c>
       <c r="F80">
-        <v>14953.302</v>
+        <v>15145.011</v>
       </c>
       <c r="G80">
         <v>2818.9</v>
@@ -7981,28 +7981,28 @@
         <v>10511.5</v>
       </c>
       <c r="M80">
-        <v>752.1510906000001</v>
+        <v>761.7940533000001</v>
       </c>
       <c r="N80">
-        <v>9759.3489094</v>
+        <v>9749.7059467</v>
       </c>
       <c r="O80">
-        <v>1854.276292786</v>
+        <v>1852.444129873</v>
       </c>
       <c r="P80">
-        <v>7905.072616613999</v>
+        <v>7897.261816827</v>
       </c>
       <c r="Q80">
-        <v>8289.572616613999</v>
+        <v>8281.761816827</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2147717046235595</v>
+        <v>0.2224231251864618</v>
       </c>
       <c r="T80">
-        <v>3.094776110592097</v>
+        <v>3.234914565269564</v>
       </c>
       <c r="U80">
         <v>0.0503</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>13.97525062632675</v>
+        <v>13.79834871966439</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07889582628915698</v>
+        <v>0.07876233756113085</v>
       </c>
       <c r="C81">
-        <v>8421.759529777039</v>
+        <v>8314.073904670709</v>
       </c>
       <c r="D81">
-        <v>20747.87052977704</v>
+        <v>20831.89390467071</v>
       </c>
       <c r="E81">
-        <v>9232.411000000002</v>
+        <v>9424.120000000001</v>
       </c>
       <c r="F81">
-        <v>15145.011</v>
+        <v>15336.72</v>
       </c>
       <c r="G81">
         <v>2818.9</v>
@@ -8063,28 +8063,28 @@
         <v>10511.5</v>
       </c>
       <c r="M81">
-        <v>761.7940533000001</v>
+        <v>771.437016</v>
       </c>
       <c r="N81">
-        <v>9749.7059467</v>
+        <v>9740.062984</v>
       </c>
       <c r="O81">
-        <v>1852.444129873</v>
+        <v>1850.61196696</v>
       </c>
       <c r="P81">
-        <v>7897.261816827</v>
+        <v>7889.45101704</v>
       </c>
       <c r="Q81">
-        <v>8281.761816827</v>
+        <v>8273.951017039999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2224231251864618</v>
+        <v>0.2308396878056543</v>
       </c>
       <c r="T81">
-        <v>3.234914565269564</v>
+        <v>3.389066865414778</v>
       </c>
       <c r="U81">
         <v>0.0503</v>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>13.79834871966439</v>
+        <v>13.62586936066858</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07876233756113085</v>
+        <v>0.07862884883310475</v>
       </c>
       <c r="C82">
-        <v>8314.073904670709</v>
+        <v>8207.071591580336</v>
       </c>
       <c r="D82">
-        <v>20831.89390467071</v>
+        <v>20916.60059158034</v>
       </c>
       <c r="E82">
-        <v>9424.120000000001</v>
+        <v>9615.829000000002</v>
       </c>
       <c r="F82">
-        <v>15336.72</v>
+        <v>15528.429</v>
       </c>
       <c r="G82">
         <v>2818.9</v>
@@ -8145,28 +8145,28 @@
         <v>10511.5</v>
       </c>
       <c r="M82">
-        <v>771.437016</v>
+        <v>781.0799787000001</v>
       </c>
       <c r="N82">
-        <v>9740.062984</v>
+        <v>9730.4200213</v>
       </c>
       <c r="O82">
-        <v>1850.61196696</v>
+        <v>1848.779804047</v>
       </c>
       <c r="P82">
-        <v>7889.45101704</v>
+        <v>7881.640217253</v>
       </c>
       <c r="Q82">
-        <v>8273.951017039999</v>
+        <v>8266.140217253</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2308396878056543</v>
+        <v>0.2401422043847619</v>
       </c>
       <c r="T82">
-        <v>3.389066865414778</v>
+        <v>3.559445723470015</v>
       </c>
       <c r="U82">
         <v>0.0503</v>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>13.62586936066858</v>
+        <v>13.45764875127761</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07862884883310475</v>
+        <v>0.07849536010507863</v>
       </c>
       <c r="C83">
-        <v>8207.071591580336</v>
+        <v>8100.760959991847</v>
       </c>
       <c r="D83">
-        <v>20916.60059158034</v>
+        <v>21001.99895999185</v>
       </c>
       <c r="E83">
-        <v>9615.829000000002</v>
+        <v>9807.538000000002</v>
       </c>
       <c r="F83">
-        <v>15528.429</v>
+        <v>15720.138</v>
       </c>
       <c r="G83">
         <v>2818.9</v>
@@ -8227,28 +8227,28 @@
         <v>10511.5</v>
       </c>
       <c r="M83">
-        <v>781.0799787000001</v>
+        <v>790.7229414000001</v>
       </c>
       <c r="N83">
-        <v>9730.4200213</v>
+        <v>9720.777058600001</v>
       </c>
       <c r="O83">
-        <v>1848.779804047</v>
+        <v>1846.947641134</v>
       </c>
       <c r="P83">
-        <v>7881.640217253</v>
+        <v>7873.829417466</v>
       </c>
       <c r="Q83">
-        <v>8266.140217253</v>
+        <v>8258.329417466</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2401422043847619</v>
+        <v>0.2504783339171035</v>
       </c>
       <c r="T83">
-        <v>3.559445723470015</v>
+        <v>3.748755565753611</v>
       </c>
       <c r="U83">
         <v>0.0503</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>13.45764875127761</v>
+        <v>13.29353108357911</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07849536010507863</v>
+        <v>0.0783618713770525</v>
       </c>
       <c r="C84">
-        <v>8100.760959991847</v>
+        <v>7995.15051663534</v>
       </c>
       <c r="D84">
-        <v>21001.99895999185</v>
+        <v>21088.09751663534</v>
       </c>
       <c r="E84">
-        <v>9807.538000000002</v>
+        <v>9999.247000000003</v>
       </c>
       <c r="F84">
-        <v>15720.138</v>
+        <v>15911.847</v>
       </c>
       <c r="G84">
         <v>2818.9</v>
@@ -8309,28 +8309,28 @@
         <v>10511.5</v>
       </c>
       <c r="M84">
-        <v>790.7229414000001</v>
+        <v>800.3659041000001</v>
       </c>
       <c r="N84">
-        <v>9720.777058600001</v>
+        <v>9711.134095900001</v>
       </c>
       <c r="O84">
-        <v>1846.947641134</v>
+        <v>1845.115478221</v>
       </c>
       <c r="P84">
-        <v>7873.829417466</v>
+        <v>7866.018617679001</v>
       </c>
       <c r="Q84">
-        <v>8258.329417466</v>
+        <v>8250.518617679001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2504783339171035</v>
+        <v>0.2620304786885442</v>
       </c>
       <c r="T84">
-        <v>3.748755565753611</v>
+        <v>3.960337154188219</v>
       </c>
       <c r="U84">
         <v>0.0503</v>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>13.29353108357911</v>
+        <v>13.13336805847574</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0783618713770525</v>
+        <v>0.07822838264902637</v>
       </c>
       <c r="C85">
-        <v>7995.15051663534</v>
+        <v>7890.248908309901</v>
       </c>
       <c r="D85">
-        <v>21088.09751663534</v>
+        <v>21174.9049083099</v>
       </c>
       <c r="E85">
-        <v>9999.247000000003</v>
+        <v>10190.956</v>
       </c>
       <c r="F85">
-        <v>15911.847</v>
+        <v>16103.556</v>
       </c>
       <c r="G85">
         <v>2818.9</v>
@@ -8391,28 +8391,28 @@
         <v>10511.5</v>
       </c>
       <c r="M85">
-        <v>800.3659041000001</v>
+        <v>810.0088668000001</v>
       </c>
       <c r="N85">
-        <v>9711.134095900001</v>
+        <v>9701.491133199999</v>
       </c>
       <c r="O85">
-        <v>1845.115478221</v>
+        <v>1843.283315308</v>
       </c>
       <c r="P85">
-        <v>7866.018617679001</v>
+        <v>7858.207817891999</v>
       </c>
       <c r="Q85">
-        <v>8250.518617679001</v>
+        <v>8242.707817891998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2620304786885442</v>
+        <v>0.275026641556415</v>
       </c>
       <c r="T85">
-        <v>3.960337154188219</v>
+        <v>4.198366441177153</v>
       </c>
       <c r="U85">
         <v>0.0503</v>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>13.13336805847574</v>
+        <v>12.97701843873198</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07822838264902639</v>
+        <v>0.07809489392100026</v>
       </c>
       <c r="C86">
-        <v>7890.248908309892</v>
+        <v>7786.064924778408</v>
       </c>
       <c r="D86">
-        <v>21174.90490830989</v>
+        <v>21262.42992477841</v>
       </c>
       <c r="E86">
-        <v>10190.956</v>
+        <v>10382.665</v>
       </c>
       <c r="F86">
-        <v>16103.556</v>
+        <v>16295.265</v>
       </c>
       <c r="G86">
         <v>2818.9</v>
@@ -8473,28 +8473,28 @@
         <v>10511.5</v>
       </c>
       <c r="M86">
-        <v>810.0088668</v>
+        <v>819.6518295000001</v>
       </c>
       <c r="N86">
-        <v>9701.491133199999</v>
+        <v>9691.848170499999</v>
       </c>
       <c r="O86">
-        <v>1843.283315308</v>
+        <v>1841.451152395</v>
       </c>
       <c r="P86">
-        <v>7858.207817891999</v>
+        <v>7850.397018104999</v>
       </c>
       <c r="Q86">
-        <v>8242.707817891998</v>
+        <v>8234.897018104999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2750266415564149</v>
+        <v>0.2897556261400017</v>
       </c>
       <c r="T86">
-        <v>4.19836644117715</v>
+        <v>4.468132966431274</v>
       </c>
       <c r="U86">
         <v>0.0503</v>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>12.97701843873198</v>
+        <v>12.82434763357043</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07809489392100026</v>
+        <v>0.07796140519297415</v>
       </c>
       <c r="C87">
-        <v>7786.064924778408</v>
+        <v>7682.607501734474</v>
       </c>
       <c r="D87">
-        <v>21262.42992477841</v>
+        <v>21350.68150173447</v>
       </c>
       <c r="E87">
-        <v>10382.665</v>
+        <v>10574.374</v>
       </c>
       <c r="F87">
-        <v>16295.265</v>
+        <v>16486.974</v>
       </c>
       <c r="G87">
         <v>2818.9</v>
@@ -8555,28 +8555,28 @@
         <v>10511.5</v>
       </c>
       <c r="M87">
-        <v>819.6518295000001</v>
+        <v>829.2947922000001</v>
       </c>
       <c r="N87">
-        <v>9691.848170499999</v>
+        <v>9682.2052078</v>
       </c>
       <c r="O87">
-        <v>1841.451152395</v>
+        <v>1839.618989482</v>
       </c>
       <c r="P87">
-        <v>7850.397018104999</v>
+        <v>7842.586218318</v>
       </c>
       <c r="Q87">
-        <v>8234.897018104999</v>
+        <v>8227.086218318</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2897556261400017</v>
+        <v>0.3065887513783868</v>
       </c>
       <c r="T87">
-        <v>4.468132966431274</v>
+        <v>4.776437566721703</v>
       </c>
       <c r="U87">
         <v>0.0503</v>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>12.82434763357043</v>
+        <v>12.67522731224984</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07796140519297415</v>
+        <v>0.07782791646494802</v>
       </c>
       <c r="C88">
-        <v>7682.607501734474</v>
+        <v>7579.885723843559</v>
       </c>
       <c r="D88">
-        <v>21350.68150173447</v>
+        <v>21439.66872384356</v>
       </c>
       <c r="E88">
-        <v>10574.374</v>
+        <v>10766.083</v>
       </c>
       <c r="F88">
-        <v>16486.974</v>
+        <v>16678.683</v>
       </c>
       <c r="G88">
         <v>2818.9</v>
@@ -8637,28 +8637,28 @@
         <v>10511.5</v>
       </c>
       <c r="M88">
-        <v>829.2947922000001</v>
+        <v>838.9377549</v>
       </c>
       <c r="N88">
-        <v>9682.2052078</v>
+        <v>9672.5622451</v>
       </c>
       <c r="O88">
-        <v>1839.618989482</v>
+        <v>1837.786826569</v>
       </c>
       <c r="P88">
-        <v>7842.586218318</v>
+        <v>7834.775418531</v>
       </c>
       <c r="Q88">
-        <v>8227.086218318</v>
+        <v>8219.275418531</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3065887513783868</v>
+        <v>0.3260115881919078</v>
       </c>
       <c r="T88">
-        <v>4.776437566721703</v>
+        <v>5.132173643979888</v>
       </c>
       <c r="U88">
         <v>0.0503</v>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>12.67522731224984</v>
+        <v>12.52953504429295</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07782791646494802</v>
+        <v>0.07769442773692192</v>
       </c>
       <c r="C89">
-        <v>7579.885723843559</v>
+        <v>7477.908827860392</v>
       </c>
       <c r="D89">
-        <v>21439.66872384356</v>
+        <v>21529.40082786039</v>
       </c>
       <c r="E89">
-        <v>10766.083</v>
+        <v>10957.792</v>
       </c>
       <c r="F89">
-        <v>16678.683</v>
+        <v>16870.392</v>
       </c>
       <c r="G89">
         <v>2818.9</v>
@@ -8719,28 +8719,28 @@
         <v>10511.5</v>
       </c>
       <c r="M89">
-        <v>838.9377549</v>
+        <v>848.5807176</v>
       </c>
       <c r="N89">
-        <v>9672.5622451</v>
+        <v>9662.9192824</v>
       </c>
       <c r="O89">
-        <v>1837.786826569</v>
+        <v>1835.954663656</v>
       </c>
       <c r="P89">
-        <v>7834.775418531</v>
+        <v>7826.964618744</v>
       </c>
       <c r="Q89">
-        <v>8219.275418531</v>
+        <v>8211.464618744001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3260115881919078</v>
+        <v>0.3486715644743493</v>
       </c>
       <c r="T89">
-        <v>5.132173643979888</v>
+        <v>5.547199067447774</v>
       </c>
       <c r="U89">
         <v>0.0503</v>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>12.52953504429295</v>
+        <v>12.38715396424417</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07769442773692192</v>
+        <v>0.0775609390088958</v>
       </c>
       <c r="C90">
-        <v>7477.908827860392</v>
+        <v>7376.686205825186</v>
       </c>
       <c r="D90">
-        <v>21529.40082786039</v>
+        <v>21619.88720582519</v>
       </c>
       <c r="E90">
-        <v>10957.792</v>
+        <v>11149.501</v>
       </c>
       <c r="F90">
-        <v>16870.392</v>
+        <v>17062.101</v>
       </c>
       <c r="G90">
         <v>2818.9</v>
@@ -8801,28 +8801,28 @@
         <v>10511.5</v>
       </c>
       <c r="M90">
-        <v>848.5807176</v>
+        <v>858.2236803000001</v>
       </c>
       <c r="N90">
-        <v>9662.9192824</v>
+        <v>9653.2763197</v>
       </c>
       <c r="O90">
-        <v>1835.954663656</v>
+        <v>1834.122500743</v>
       </c>
       <c r="P90">
-        <v>7826.964618744</v>
+        <v>7819.153818957</v>
       </c>
       <c r="Q90">
-        <v>8211.464618744001</v>
+        <v>8203.653818957</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3486715644743493</v>
+        <v>0.3754515364445072</v>
       </c>
       <c r="T90">
-        <v>5.547199067447774</v>
+        <v>6.037683658818908</v>
       </c>
       <c r="U90">
         <v>0.0503</v>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>12.38715396424417</v>
+        <v>12.24797245902794</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0775609390088958</v>
+        <v>0.07742745028086967</v>
       </c>
       <c r="C91">
-        <v>7376.686205825186</v>
+        <v>7276.22740834055</v>
       </c>
       <c r="D91">
-        <v>21619.88720582519</v>
+        <v>21711.13740834055</v>
       </c>
       <c r="E91">
-        <v>11149.501</v>
+        <v>11341.21</v>
       </c>
       <c r="F91">
-        <v>17062.101</v>
+        <v>17253.81</v>
       </c>
       <c r="G91">
         <v>2818.9</v>
@@ -8883,28 +8883,28 @@
         <v>10511.5</v>
       </c>
       <c r="M91">
-        <v>858.2236803000001</v>
+        <v>867.8666430000001</v>
       </c>
       <c r="N91">
-        <v>9653.2763197</v>
+        <v>9643.633357000001</v>
       </c>
       <c r="O91">
-        <v>1834.122500743</v>
+        <v>1832.29033783</v>
       </c>
       <c r="P91">
-        <v>7819.153818957</v>
+        <v>7811.343019170001</v>
       </c>
       <c r="Q91">
-        <v>8203.653818957</v>
+        <v>8195.843019170001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3754515364445072</v>
+        <v>0.4075875028086968</v>
       </c>
       <c r="T91">
-        <v>6.037683658818908</v>
+        <v>6.626265168464272</v>
       </c>
       <c r="U91">
         <v>0.0503</v>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>12.24797245902794</v>
+        <v>12.11188387614985</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07742745028086967</v>
+        <v>0.07729396155284356</v>
       </c>
       <c r="C92">
-        <v>7276.22740834055</v>
+        <v>7176.542147931919</v>
       </c>
       <c r="D92">
-        <v>21711.13740834055</v>
+        <v>21803.16114793192</v>
       </c>
       <c r="E92">
-        <v>11341.21</v>
+        <v>11532.919</v>
       </c>
       <c r="F92">
-        <v>17253.81</v>
+        <v>17445.519</v>
       </c>
       <c r="G92">
         <v>2818.9</v>
@@ -8965,28 +8965,28 @@
         <v>10511.5</v>
       </c>
       <c r="M92">
-        <v>867.8666430000001</v>
+        <v>877.5096057</v>
       </c>
       <c r="N92">
-        <v>9643.633357000001</v>
+        <v>9633.990394300001</v>
       </c>
       <c r="O92">
-        <v>1832.29033783</v>
+        <v>1830.458174917</v>
       </c>
       <c r="P92">
-        <v>7811.343019170001</v>
+        <v>7803.532219383001</v>
       </c>
       <c r="Q92">
-        <v>8195.843019170001</v>
+        <v>8188.032219383001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4075875028086968</v>
+        <v>0.4468647950315952</v>
       </c>
       <c r="T92">
-        <v>6.626265168464272</v>
+        <v>7.345642569141937</v>
       </c>
       <c r="U92">
         <v>0.0503</v>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>12.11188387614985</v>
+        <v>11.97878625113722</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07729396155284356</v>
+        <v>0.07716047282481744</v>
       </c>
       <c r="C93">
-        <v>7176.542147931919</v>
+        <v>7077.640302493779</v>
       </c>
       <c r="D93">
-        <v>21803.16114793192</v>
+        <v>21895.96830249378</v>
       </c>
       <c r="E93">
-        <v>11532.919</v>
+        <v>11724.628</v>
       </c>
       <c r="F93">
-        <v>17445.519</v>
+        <v>17637.228</v>
       </c>
       <c r="G93">
         <v>2818.9</v>
@@ -9047,28 +9047,28 @@
         <v>10511.5</v>
       </c>
       <c r="M93">
-        <v>877.5096057</v>
+        <v>887.1525684000001</v>
       </c>
       <c r="N93">
-        <v>9633.990394300001</v>
+        <v>9624.347431599999</v>
       </c>
       <c r="O93">
-        <v>1830.458174917</v>
+        <v>1828.626012004</v>
       </c>
       <c r="P93">
-        <v>7803.532219383001</v>
+        <v>7795.721419596</v>
       </c>
       <c r="Q93">
-        <v>8188.032219383001</v>
+        <v>8180.221419596</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4468647950315952</v>
+        <v>0.4959614103102182</v>
       </c>
       <c r="T93">
-        <v>7.345642569141937</v>
+        <v>8.244864319989022</v>
       </c>
       <c r="U93">
         <v>0.0503</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>11.97878625113722</v>
+        <v>11.84858205275529</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07716047282481744</v>
+        <v>0.07702698409679132</v>
       </c>
       <c r="C94">
-        <v>7077.640302493779</v>
+        <v>6979.531918824207</v>
       </c>
       <c r="D94">
-        <v>21895.96830249378</v>
+        <v>21989.56891882421</v>
       </c>
       <c r="E94">
-        <v>11724.628</v>
+        <v>11916.337</v>
       </c>
       <c r="F94">
-        <v>17637.228</v>
+        <v>17828.937</v>
       </c>
       <c r="G94">
         <v>2818.9</v>
@@ -9129,28 +9129,28 @@
         <v>10511.5</v>
       </c>
       <c r="M94">
-        <v>887.1525684000001</v>
+        <v>896.7955311000001</v>
       </c>
       <c r="N94">
-        <v>9624.347431599999</v>
+        <v>9614.704468899999</v>
       </c>
       <c r="O94">
-        <v>1828.626012004</v>
+        <v>1826.793849091</v>
       </c>
       <c r="P94">
-        <v>7795.721419596</v>
+        <v>7787.910619808999</v>
       </c>
       <c r="Q94">
-        <v>8180.221419596</v>
+        <v>8172.410619808999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4959614103102182</v>
+        <v>0.559085629954162</v>
       </c>
       <c r="T94">
-        <v>8.244864319989022</v>
+        <v>9.401006571078128</v>
       </c>
       <c r="U94">
         <v>0.0503</v>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>11.84858205275529</v>
+        <v>11.72117794466115</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07702698409679132</v>
+        <v>0.07689349536876519</v>
       </c>
       <c r="C95">
-        <v>6979.531918824207</v>
+        <v>6882.227216250525</v>
       </c>
       <c r="D95">
-        <v>21989.56891882421</v>
+        <v>22083.97321625053</v>
       </c>
       <c r="E95">
-        <v>11916.337</v>
+        <v>12108.046</v>
       </c>
       <c r="F95">
-        <v>17828.937</v>
+        <v>18020.646</v>
       </c>
       <c r="G95">
         <v>2818.9</v>
@@ -9211,28 +9211,28 @@
         <v>10511.5</v>
       </c>
       <c r="M95">
-        <v>896.7955311000001</v>
+        <v>906.4384938000002</v>
       </c>
       <c r="N95">
-        <v>9614.704468899999</v>
+        <v>9605.0615062</v>
       </c>
       <c r="O95">
-        <v>1826.793849091</v>
+        <v>1824.961686178</v>
       </c>
       <c r="P95">
-        <v>7787.910619808999</v>
+        <v>7780.099820022</v>
       </c>
       <c r="Q95">
-        <v>8172.410619808999</v>
+        <v>8164.599820022</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.559085629954162</v>
+        <v>0.6432512561460871</v>
       </c>
       <c r="T95">
-        <v>9.401006571078128</v>
+        <v>10.94252957253027</v>
       </c>
       <c r="U95">
         <v>0.0503</v>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>11.72117794466115</v>
+        <v>11.59648456227113</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07689349536876519</v>
+        <v>0.07676000664073908</v>
       </c>
       <c r="C96">
-        <v>6882.227216250525</v>
+        <v>6785.736590348704</v>
       </c>
       <c r="D96">
-        <v>22083.97321625053</v>
+        <v>22179.19159034871</v>
       </c>
       <c r="E96">
-        <v>12108.046</v>
+        <v>12299.755</v>
       </c>
       <c r="F96">
-        <v>18020.646</v>
+        <v>18212.355</v>
       </c>
       <c r="G96">
         <v>2818.9</v>
@@ -9293,28 +9293,28 @@
         <v>10511.5</v>
       </c>
       <c r="M96">
-        <v>906.4384938000002</v>
+        <v>916.0814565000002</v>
       </c>
       <c r="N96">
-        <v>9605.0615062</v>
+        <v>9595.4185435</v>
       </c>
       <c r="O96">
-        <v>1824.961686178</v>
+        <v>1823.129523265</v>
       </c>
       <c r="P96">
-        <v>7780.099820022</v>
+        <v>7772.289020235</v>
       </c>
       <c r="Q96">
-        <v>8164.599820022</v>
+        <v>8156.789020235</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6432512561460871</v>
+        <v>0.7610831328147825</v>
       </c>
       <c r="T96">
-        <v>10.94252957253027</v>
+        <v>13.10066177456327</v>
       </c>
       <c r="U96">
         <v>0.0503</v>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>11.59648456227113</v>
+        <v>11.47441630372091</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07676000664073908</v>
+        <v>0.07662651791271297</v>
       </c>
       <c r="C97">
-        <v>6785.736590348704</v>
+        <v>6690.070616759487</v>
       </c>
       <c r="D97">
-        <v>22179.19159034871</v>
+        <v>22275.23461675949</v>
       </c>
       <c r="E97">
-        <v>12299.755</v>
+        <v>12491.464</v>
       </c>
       <c r="F97">
-        <v>18212.355</v>
+        <v>18404.064</v>
       </c>
       <c r="G97">
         <v>2818.9</v>
@@ -9375,28 +9375,28 @@
         <v>10511.5</v>
       </c>
       <c r="M97">
-        <v>916.0814565000002</v>
+        <v>925.7244192000001</v>
       </c>
       <c r="N97">
-        <v>9595.4185435</v>
+        <v>9585.7755808</v>
       </c>
       <c r="O97">
-        <v>1823.129523265</v>
+        <v>1821.297360352</v>
       </c>
       <c r="P97">
-        <v>7772.289020235</v>
+        <v>7764.478220448</v>
       </c>
       <c r="Q97">
-        <v>8156.789020235</v>
+        <v>8148.978220448</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7610831328147825</v>
+        <v>0.9378309478178257</v>
       </c>
       <c r="T97">
-        <v>13.10066177456327</v>
+        <v>16.33786007761278</v>
       </c>
       <c r="U97">
         <v>0.0503</v>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>11.47441630372091</v>
+        <v>11.35489113389049</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07662651791271297</v>
+        <v>0.07649302918468684</v>
       </c>
       <c r="C98">
-        <v>6690.070616759487</v>
+        <v>6595.24005510399</v>
       </c>
       <c r="D98">
-        <v>22275.23461675949</v>
+        <v>22372.11305510399</v>
       </c>
       <c r="E98">
-        <v>12491.464</v>
+        <v>12683.173</v>
       </c>
       <c r="F98">
-        <v>18404.064</v>
+        <v>18595.773</v>
       </c>
       <c r="G98">
         <v>2818.9</v>
@@ -9457,28 +9457,28 @@
         <v>10511.5</v>
       </c>
       <c r="M98">
-        <v>925.7244192000001</v>
+        <v>935.3673819000001</v>
       </c>
       <c r="N98">
-        <v>9585.7755808</v>
+        <v>9576.1326181</v>
       </c>
       <c r="O98">
-        <v>1821.297360352</v>
+        <v>1819.465197439</v>
       </c>
       <c r="P98">
-        <v>7764.478220448</v>
+        <v>7756.667420661001</v>
       </c>
       <c r="Q98">
-        <v>8148.978220448</v>
+        <v>8141.167420661001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9378309478178233</v>
+        <v>1.23241063948956</v>
       </c>
       <c r="T98">
-        <v>16.33786007761273</v>
+        <v>21.73319058269522</v>
       </c>
       <c r="U98">
         <v>0.0503</v>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>11.35489113389049</v>
+        <v>11.23783040055141</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07649302918468684</v>
+        <v>0.07635954045666073</v>
       </c>
       <c r="C99">
-        <v>6595.24005510399</v>
+        <v>6501.255853001971</v>
       </c>
       <c r="D99">
-        <v>22372.11305510399</v>
+        <v>22469.83785300197</v>
       </c>
       <c r="E99">
-        <v>12683.173</v>
+        <v>12874.882</v>
       </c>
       <c r="F99">
-        <v>18595.773</v>
+        <v>18787.482</v>
       </c>
       <c r="G99">
         <v>2818.9</v>
@@ -9539,28 +9539,28 @@
         <v>10511.5</v>
       </c>
       <c r="M99">
-        <v>935.3673819000001</v>
+        <v>945.0103445999999</v>
       </c>
       <c r="N99">
-        <v>9576.1326181</v>
+        <v>9566.489655400001</v>
       </c>
       <c r="O99">
-        <v>1819.465197439</v>
+        <v>1817.633034526</v>
       </c>
       <c r="P99">
-        <v>7756.667420661001</v>
+        <v>7748.856620874</v>
       </c>
       <c r="Q99">
-        <v>8141.167420661001</v>
+        <v>8133.356620874</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.23241063948956</v>
+        <v>1.821570022833035</v>
       </c>
       <c r="T99">
-        <v>21.73319058269522</v>
+        <v>32.52385159286018</v>
       </c>
       <c r="U99">
         <v>0.0503</v>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>11.23783040055141</v>
+        <v>11.12315866177027</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07635954045666073</v>
+        <v>0.07622605172863461</v>
       </c>
       <c r="C100">
-        <v>6501.255853001971</v>
+        <v>6408.129150195902</v>
       </c>
       <c r="D100">
-        <v>22469.83785300197</v>
+        <v>22568.4201501959</v>
       </c>
       <c r="E100">
-        <v>12874.882</v>
+        <v>13066.591</v>
       </c>
       <c r="F100">
-        <v>18787.482</v>
+        <v>18979.191</v>
       </c>
       <c r="G100">
         <v>2818.9</v>
@@ -9621,28 +9621,28 @@
         <v>10511.5</v>
       </c>
       <c r="M100">
-        <v>945.0103445999999</v>
+        <v>954.6533073000001</v>
       </c>
       <c r="N100">
-        <v>9566.489655400001</v>
+        <v>9556.846692700001</v>
       </c>
       <c r="O100">
-        <v>1817.633034526</v>
+        <v>1815.800871613</v>
       </c>
       <c r="P100">
-        <v>7748.856620874</v>
+        <v>7741.045821087</v>
       </c>
       <c r="Q100">
-        <v>8133.356620874</v>
+        <v>8125.545821087</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.821570022833035</v>
+        <v>3.589048172863457</v>
       </c>
       <c r="T100">
-        <v>32.52385159286018</v>
+        <v>64.89583462335509</v>
       </c>
       <c r="U100">
         <v>0.0503</v>
@@ -9659,91 +9659,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>11.12315866177027</v>
+        <v>11.01080352377259</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07622605172863461</v>
-      </c>
-      <c r="C101">
-        <v>6408.129150195902</v>
-      </c>
-      <c r="D101">
-        <v>22568.4201501959</v>
-      </c>
-      <c r="E101">
-        <v>13066.591</v>
-      </c>
-      <c r="F101">
-        <v>18979.191</v>
-      </c>
-      <c r="G101">
-        <v>2818.9</v>
-      </c>
-      <c r="H101">
-        <v>13258.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10896</v>
-      </c>
-      <c r="K101">
-        <v>384.5</v>
-      </c>
-      <c r="L101">
-        <v>10511.5</v>
-      </c>
-      <c r="M101">
-        <v>954.6533073000001</v>
-      </c>
-      <c r="N101">
-        <v>9556.846692700001</v>
-      </c>
-      <c r="O101">
-        <v>1815.800871613</v>
-      </c>
-      <c r="P101">
-        <v>7741.045821087</v>
-      </c>
-      <c r="Q101">
-        <v>8125.545821087</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.589048172863457</v>
-      </c>
-      <c r="T101">
-        <v>64.89583462335509</v>
-      </c>
-      <c r="U101">
-        <v>0.0503</v>
-      </c>
-      <c r="V101">
-        <v>0.19</v>
-      </c>
-      <c r="W101">
-        <v>0.040743</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Aaa/AAA</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>11.01080352377259</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
